--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="matchs" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="matchs" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">matchs!$A$1:$F$116</definedName>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="40">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -94,9 +94,6 @@
     <t xml:space="preserve">Jasmine</t>
   </si>
   <si>
-    <t xml:space="preserve">BenjaminC </t>
-  </si>
-  <si>
     <t xml:space="preserve">Tanguy</t>
   </si>
   <si>
@@ -143,15 +140,19 @@
   </si>
   <si>
     <t xml:space="preserve">PhilippeA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DenisB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -255,7 +256,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -304,6 +305,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -316,119 +325,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="24" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.55859375" defaultRowHeight="24" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.17"/>
@@ -833,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>10</v>
@@ -847,13 +750,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>10</v>
@@ -1104,7 +1007,7 @@
         <v>46052</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>13</v>
@@ -1127,10 +1030,10 @@
         <v>20</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>16</v>
@@ -1267,10 +1170,10 @@
         <v>16</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>17</v>
@@ -1290,7 +1193,7 @@
         <v>20</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>13</v>
@@ -1304,16 +1207,16 @@
         <v>46055</v>
       </c>
       <c r="B44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>10</v>
@@ -1327,13 +1230,13 @@
         <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>10</v>
@@ -1370,10 +1273,10 @@
         <v>14</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>10</v>
@@ -1384,16 +1287,16 @@
         <v>46057</v>
       </c>
       <c r="B48" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="E48" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>10</v>
@@ -1430,7 +1333,7 @@
         <v>16</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>20</v>
@@ -1450,10 +1353,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>10</v>
@@ -1470,7 +1373,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>20</v>
@@ -1524,7 +1427,7 @@
         <v>46058</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>16</v>
@@ -1553,7 +1456,7 @@
         <v>7</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>10</v>
@@ -1573,7 +1476,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>11</v>
@@ -1587,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>11</v>
@@ -1613,7 +1516,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>11</v>
@@ -1667,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>9</v>
@@ -1847,13 +1750,13 @@
         <v>13</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>10</v>
@@ -1864,13 +1767,13 @@
         <v>46059</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>15</v>
@@ -1887,7 +1790,7 @@
         <v>14</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>7</v>
@@ -2084,13 +1987,13 @@
         <v>46059</v>
       </c>
       <c r="B83" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>20</v>
@@ -2124,10 +2027,10 @@
         <v>46059</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>16</v>
@@ -2164,13 +2067,13 @@
         <v>46059</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>16</v>
@@ -2233,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>10</v>
@@ -2730,10 +2633,10 @@
         <v>8</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>11</v>
@@ -2747,7 +2650,7 @@
         <v>20</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D116" s="11" t="s">
         <v>13</v>
@@ -2764,16 +2667,16 @@
         <v>46063</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F117" s="11" t="s">
         <v>10</v>
@@ -2784,16 +2687,16 @@
         <v>46063</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>11</v>
@@ -2810,7 +2713,7 @@
         <v>13</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>18</v>
@@ -2827,13 +2730,13 @@
         <v>12</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D120" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>10</v>
@@ -2853,7 +2756,7 @@
         <v>14</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>11</v>
@@ -2864,7 +2767,7 @@
         <v>46064</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C122" s="11" t="s">
         <v>15</v>
@@ -2884,7 +2787,7 @@
         <v>46064</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>8</v>
@@ -2913,7 +2816,7 @@
         <v>8</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>11</v>
@@ -2944,7 +2847,7 @@
         <v>46064</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C126" s="11" t="s">
         <v>8</v>
@@ -2987,10 +2890,10 @@
         <v>9</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E128" s="11" t="s">
         <v>7</v>
@@ -3007,13 +2910,13 @@
         <v>6</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D129" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>10</v>
@@ -3033,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>11</v>
@@ -3053,7 +2956,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>11</v>
@@ -3067,13 +2970,13 @@
         <v>13</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>11</v>
@@ -3087,19 +2990,19 @@
         <v>19</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="n">
         <v>46069</v>
       </c>
@@ -3107,7 +3010,7 @@
         <v>16</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D134" s="11" t="s">
         <v>7</v>
@@ -3119,7 +3022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="n">
         <v>46069</v>
       </c>
@@ -3130,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E135" s="11" t="s">
         <v>18</v>
@@ -3139,285 +3042,727 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7" t="n">
+    <row r="136" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="10" t="n">
         <v>46071</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="B136" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7" t="n">
+      <c r="E136" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="10" t="n">
         <v>46071</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" s="1" t="s">
+      <c r="B137" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="D137" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7" t="n">
+      <c r="F137" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="10" t="n">
         <v>46071</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="1" t="s">
+      <c r="C138" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7" t="n">
+      <c r="E138" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F138" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="10" t="n">
         <v>46071</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="1" t="s">
+      <c r="B139" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7" t="n">
+      <c r="F139" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="10" t="n">
         <v>46071</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" s="1" t="s">
+      <c r="B140" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="D140" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F140" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7" t="n">
+      <c r="F140" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="10" t="n">
         <v>46072</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="B141" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F141" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7" t="n">
+      <c r="F142" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="10" t="n">
         <v>46072</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="1" t="s">
+      <c r="B143" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F143" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B144" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="C144" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E144" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F145" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E147" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F148" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="10" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B151" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="C151" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B152" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F142" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" s="1" t="s">
+      <c r="C152" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E152" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F152" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F156" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F158" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="12" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="12" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" s="1" t="s">
+      <c r="C163" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F143" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D147" s="1" t="s">
+      <c r="E163" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="12" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7" t="n">
-        <v>46072</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="E164" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="12" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F165" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="12" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="13"/>
+    </row>
+    <row r="168" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="13"/>
+    </row>
+    <row r="169" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="13"/>
+    </row>
+    <row r="170" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="13"/>
+    </row>
+    <row r="171" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="13"/>
+    </row>
+    <row r="172" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="13"/>
+    </row>
+    <row r="173" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="13"/>
+    </row>
+    <row r="174" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="13"/>
+    </row>
+    <row r="175" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="13"/>
+    </row>
+    <row r="176" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="13"/>
+    </row>
+    <row r="177" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="13"/>
+    </row>
+    <row r="178" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="13"/>
+    </row>
+    <row r="179" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="13"/>
+    </row>
+    <row r="180" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="13"/>
+    </row>
+    <row r="181" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="13"/>
+    </row>
+    <row r="182" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="13"/>
+    </row>
+    <row r="183" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="13"/>
+    </row>
+    <row r="184" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="13"/>
+    </row>
+    <row r="185" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="13"/>
+    </row>
+    <row r="186" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="13"/>
+    </row>
+    <row r="187" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="13"/>
+    </row>
+    <row r="188" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="13"/>
+    </row>
+    <row r="189" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="13"/>
+    </row>
+    <row r="190" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="13"/>
+    </row>
+    <row r="191" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="13"/>
+    </row>
+    <row r="192" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="13"/>
+    </row>
+    <row r="193" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="13"/>
+    </row>
+    <row r="194" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="13"/>
+    </row>
+    <row r="195" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="13"/>
+    </row>
+    <row r="196" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="13"/>
+    </row>
+    <row r="197" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="13"/>
+    </row>
+    <row r="198" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="13"/>
+    </row>
+    <row r="199" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="13"/>
+    </row>
+    <row r="200" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="13"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="40">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -149,10 +149,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -256,7 +255,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -305,14 +304,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,7 +322,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="10.55859375" defaultRowHeight="24" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="24" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.17"/>
@@ -3323,7 +3314,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="12" t="n">
+      <c r="A150" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B150" s="11" t="s">
@@ -3343,7 +3334,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="12" t="n">
+      <c r="A151" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B151" s="11" t="s">
@@ -3363,7 +3354,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="12" t="n">
+      <c r="A152" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B152" s="11" t="s">
@@ -3383,7 +3374,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="12" t="n">
+      <c r="A153" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B153" s="11" t="s">
@@ -3403,7 +3394,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="12" t="n">
+      <c r="A154" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B154" s="11" t="s">
@@ -3423,7 +3414,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="12" t="n">
+      <c r="A155" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B155" s="11" t="s">
@@ -3443,7 +3434,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="12" t="n">
+      <c r="A156" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B156" s="11" t="s">
@@ -3463,7 +3454,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="12" t="n">
+      <c r="A157" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B157" s="11" t="s">
@@ -3483,7 +3474,7 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="12" t="n">
+      <c r="A158" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B158" s="11" t="s">
@@ -3503,7 +3494,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="12" t="n">
+      <c r="A159" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B159" s="11" t="s">
@@ -3523,7 +3514,7 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="12" t="n">
+      <c r="A160" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B160" s="11" t="s">
@@ -3543,7 +3534,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="12" t="n">
+      <c r="A161" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B161" s="11" t="s">
@@ -3563,7 +3554,7 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="12" t="n">
+      <c r="A162" s="10" t="n">
         <v>46073</v>
       </c>
       <c r="B162" s="11" t="s">
@@ -3583,7 +3574,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="12" t="n">
+      <c r="A163" s="10" t="n">
         <v>46077</v>
       </c>
       <c r="B163" s="11" t="s">
@@ -3603,7 +3594,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="12" t="n">
+      <c r="A164" s="10" t="n">
         <v>46077</v>
       </c>
       <c r="B164" s="11" t="s">
@@ -3623,7 +3614,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="12" t="n">
+      <c r="A165" s="10" t="n">
         <v>46077</v>
       </c>
       <c r="B165" s="11" t="s">
@@ -3643,7 +3634,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="12" t="n">
+      <c r="A166" s="10" t="n">
         <v>46077</v>
       </c>
       <c r="B166" s="11" t="s">
@@ -3663,106 +3654,344 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="13"/>
+      <c r="A167" s="10" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F167" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="13"/>
+      <c r="A168" s="10" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F168" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="13"/>
+      <c r="A169" s="10" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="13"/>
+      <c r="A170" s="10" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="13"/>
+      <c r="A171" s="10" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F171" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="13"/>
+      <c r="A172" s="10" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E172" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F172" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="13"/>
+      <c r="A173" s="10" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="13"/>
+      <c r="A174" s="10" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F174" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="13"/>
+      <c r="A175" s="10" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="13"/>
+      <c r="A176" s="10" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F176" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="13"/>
+      <c r="A177" s="10" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E177" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="13"/>
+      <c r="A178" s="10" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F178" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="13"/>
+      <c r="A179" s="10" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F179" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="13"/>
+      <c r="A180" s="10" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E180" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F180" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="13"/>
+      <c r="A181" s="7"/>
     </row>
     <row r="182" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="13"/>
+      <c r="A182" s="7"/>
     </row>
     <row r="183" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="13"/>
+      <c r="A183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="13"/>
+      <c r="A184" s="7"/>
     </row>
     <row r="185" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="13"/>
+      <c r="A185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="13"/>
+      <c r="A186" s="7"/>
     </row>
     <row r="187" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="13"/>
+      <c r="A187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="13"/>
+      <c r="A188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="13"/>
+      <c r="A189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="13"/>
+      <c r="A190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="13"/>
+      <c r="A191" s="7"/>
     </row>
     <row r="192" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="13"/>
+      <c r="A192" s="7"/>
     </row>
     <row r="193" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="13"/>
+      <c r="A193" s="7"/>
     </row>
     <row r="194" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="13"/>
+      <c r="A194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="13"/>
+      <c r="A195" s="7"/>
     </row>
     <row r="196" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="13"/>
+      <c r="A196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="13"/>
+      <c r="A197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="13"/>
+      <c r="A198" s="7"/>
     </row>
     <row r="199" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="13"/>
+      <c r="A199" s="7"/>
     </row>
     <row r="200" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="13"/>
+      <c r="A200" s="7"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C5B903-1372-4102-82CC-20730EB938CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="matchs" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="matchs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">matchs!$A$1:$F$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">matchs!$A$1:$F$116</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,158 +31,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="41">
   <si>
-    <t xml:space="preserve">date</t>
+    <t>date</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge_p1</t>
+    <t>rouge_p1</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge_p2</t>
+    <t>rouge_p2</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu_p1</t>
+    <t>bleu_p1</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu_p2</t>
+    <t>bleu_p2</t>
   </si>
   <si>
-    <t xml:space="preserve">vainqueur</t>
+    <t>vainqueur</t>
   </si>
   <si>
-    <t xml:space="preserve">NathV</t>
+    <t>NathV</t>
   </si>
   <si>
-    <t xml:space="preserve">Lily</t>
+    <t>Lily</t>
   </si>
   <si>
-    <t xml:space="preserve">Roland</t>
+    <t>Roland</t>
   </si>
   <si>
-    <t xml:space="preserve">Rémi</t>
+    <t>Rémi</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu</t>
+    <t>bleu</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge</t>
+    <t>rouge</t>
   </si>
   <si>
-    <t xml:space="preserve">ManonV</t>
+    <t>ManonV</t>
   </si>
   <si>
-    <t xml:space="preserve">Lilou</t>
+    <t>Lilou</t>
   </si>
   <si>
-    <t xml:space="preserve">Paul</t>
+    <t>Paul</t>
   </si>
   <si>
-    <t xml:space="preserve">Anne-Laure P</t>
+    <t>Anne-Laure P</t>
   </si>
   <si>
-    <t xml:space="preserve">Raphaël</t>
+    <t>Raphaël</t>
   </si>
   <si>
-    <t xml:space="preserve">Benoit</t>
+    <t>Benoit</t>
   </si>
   <si>
-    <t xml:space="preserve">Julia</t>
+    <t>Julia</t>
   </si>
   <si>
-    <t xml:space="preserve">Armelle</t>
+    <t>Armelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Jules</t>
+    <t>Jules</t>
   </si>
   <si>
-    <t xml:space="preserve">BenjaminC</t>
+    <t>BenjaminC</t>
   </si>
   <si>
-    <t xml:space="preserve">Jasmine</t>
+    <t>Jasmine</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanguy</t>
+    <t>Tanguy</t>
   </si>
   <si>
-    <t xml:space="preserve">Marguerite</t>
+    <t>Marguerite</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom</t>
+    <t>Tom</t>
   </si>
   <si>
-    <t xml:space="preserve">LaureS</t>
+    <t>LaureS</t>
   </si>
   <si>
-    <t xml:space="preserve">Sabine</t>
+    <t>Sabine</t>
   </si>
   <si>
-    <t xml:space="preserve">SimonB</t>
+    <t>SimonB</t>
   </si>
   <si>
-    <t xml:space="preserve">Loïc</t>
+    <t>Loïc</t>
   </si>
   <si>
-    <t xml:space="preserve">JulieB</t>
+    <t>JulieB</t>
   </si>
   <si>
-    <t xml:space="preserve">TheoM</t>
+    <t>TheoM</t>
   </si>
   <si>
-    <t xml:space="preserve">Mountassira</t>
+    <t>Mountassira</t>
   </si>
   <si>
-    <t xml:space="preserve">EmmanuelP</t>
+    <t>EmmanuelP</t>
   </si>
   <si>
-    <t xml:space="preserve">VincentD</t>
+    <t>VincentD</t>
   </si>
   <si>
-    <t xml:space="preserve">BenjaminZ</t>
+    <t>BenjaminZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximilien</t>
+    <t>Maximilien</t>
   </si>
   <si>
-    <t xml:space="preserve">Anna</t>
+    <t>Anna</t>
   </si>
   <si>
-    <t xml:space="preserve">PhilippeA</t>
+    <t>PhilippeA</t>
   </si>
   <si>
-    <t xml:space="preserve">DenisB</t>
+    <t>DenisB</t>
+  </si>
+  <si>
+    <t>Max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="18"/>
@@ -184,7 +176,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -201,139 +193,386 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F1048576"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="24" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G204"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="10.84"/>
+    <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -353,8 +592,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
         <v>46048</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -373,8 +612,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
         <v>46048</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -393,8 +632,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
         <v>46049</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -413,8 +652,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
         <v>46049</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -433,8 +672,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
         <v>46049</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -453,8 +692,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>46049</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -473,8 +712,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>46049</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -493,8 +732,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
         <v>46049</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -513,8 +752,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
         <v>46049</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -533,8 +772,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
         <v>46049</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -553,8 +792,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
         <v>46049</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -573,8 +812,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
         <v>46049</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -593,8 +832,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
         <v>46050</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -613,8 +852,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
         <v>46050</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -633,8 +872,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
         <v>46050</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -653,8 +892,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
         <v>46050</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -673,8 +912,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
         <v>46050</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -693,8 +932,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
         <v>46051</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -713,8 +952,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
         <v>46052</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -733,8 +972,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
         <v>46052</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -753,8 +992,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="7">
         <v>46052</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -773,8 +1012,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
         <v>46052</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -793,8 +1032,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="7">
         <v>46052</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -813,8 +1052,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
         <v>46052</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -833,8 +1072,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="7">
         <v>46052</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -853,8 +1092,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
         <v>46052</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -873,8 +1112,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="7">
         <v>46052</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -893,8 +1132,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
         <v>46052</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -913,8 +1152,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="n">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="7">
         <v>46052</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -933,8 +1172,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
         <v>46052</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -953,8 +1192,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="n">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="7">
         <v>46052</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -973,8 +1212,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
         <v>46052</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -993,8 +1232,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="7">
         <v>46052</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -1013,8 +1252,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
         <v>46052</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -1033,8 +1272,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="n">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="7">
         <v>46052</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -1053,8 +1292,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
         <v>46052</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -1073,8 +1312,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="n">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="7">
         <v>46052</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1093,8 +1332,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
         <v>46052</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -1113,8 +1352,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="n">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="7">
         <v>46052</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -1133,8 +1372,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="7">
         <v>46052</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -1153,8 +1392,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="n">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="7">
         <v>46055</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -1173,8 +1412,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="7">
         <v>46055</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -1193,8 +1432,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="n">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="7">
         <v>46055</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -1213,8 +1452,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="7">
         <v>46056</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -1233,8 +1472,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="n">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="7">
         <v>46056</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -1253,8 +1492,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="7">
         <v>46056</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -1273,8 +1512,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="n">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="7">
         <v>46057</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -1293,8 +1532,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="7">
         <v>46057</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -1313,8 +1552,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="n">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="7">
         <v>46057</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -1333,8 +1572,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="7">
         <v>46057</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -1353,8 +1592,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="n">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="7">
         <v>46057</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -1373,8 +1612,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="7">
         <v>46057</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -1393,8 +1632,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="n">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="7">
         <v>46057</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -1413,8 +1652,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="7">
         <v>46058</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -1433,8 +1672,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="n">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="7">
         <v>46058</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -1453,8 +1692,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="7">
         <v>46058</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -1473,8 +1712,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="n">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="7">
         <v>46058</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -1493,8 +1732,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="7">
         <v>46058</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -1513,8 +1752,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="n">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="7">
         <v>46058</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -1533,8 +1772,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="7">
         <v>46058</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -1553,8 +1792,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="n">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="7">
         <v>46058</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -1573,8 +1812,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="7">
         <v>46058</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -1593,8 +1832,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="n">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="7">
         <v>46058</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -1613,8 +1852,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="7">
         <v>46058</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -1633,8 +1872,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="n">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="7">
         <v>46058</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -1653,8 +1892,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="7">
         <v>46058</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -1673,8 +1912,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="n">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="7">
         <v>46058</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -1693,8 +1932,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="7">
         <v>46058</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -1713,8 +1952,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="n">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="7">
         <v>46058</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -1733,8 +1972,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="7">
         <v>46059</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -1753,8 +1992,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="7">
         <v>46059</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -1773,8 +2012,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="7">
         <v>46059</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -1793,8 +2032,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="7">
         <v>46059</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -1813,8 +2052,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="7">
         <v>46059</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -1833,8 +2072,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="n">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="7">
         <v>46059</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -1853,8 +2092,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="7">
         <v>46059</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -1873,8 +2112,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="n">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="7">
         <v>46059</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -1893,8 +2132,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="7">
         <v>46059</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -1913,8 +2152,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="n">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="7">
         <v>46059</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -1933,8 +2172,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="7">
         <v>46059</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -1953,8 +2192,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="n">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="7">
         <v>46059</v>
       </c>
       <c r="B82" s="8" t="s">
@@ -1973,8 +2212,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="7">
         <v>46059</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -1993,8 +2232,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="n">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="7">
         <v>46059</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -2013,8 +2252,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="7">
         <v>46059</v>
       </c>
       <c r="B85" s="8" t="s">
@@ -2033,8 +2272,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="n">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="7">
         <v>46059</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -2053,8 +2292,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="7">
         <v>46059</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -2073,8 +2312,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="n">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="7">
         <v>46059</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -2093,8 +2332,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="7">
         <v>46059</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -2113,8 +2352,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="n">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="7">
         <v>46059</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -2133,8 +2372,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="n">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="7">
         <v>46059</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -2153,8 +2392,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="n">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="7">
         <v>46059</v>
       </c>
       <c r="B92" s="8" t="s">
@@ -2173,8 +2412,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="n">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="7">
         <v>46059</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -2193,8 +2432,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="n">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="7">
         <v>46059</v>
       </c>
       <c r="B94" s="8" t="s">
@@ -2213,8 +2452,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="n">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="7">
         <v>46059</v>
       </c>
       <c r="B95" s="8" t="s">
@@ -2233,8 +2472,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7" t="n">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="7">
         <v>46059</v>
       </c>
       <c r="B96" s="8" t="s">
@@ -2253,8 +2492,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="n">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="7">
         <v>46059</v>
       </c>
       <c r="B97" s="8" t="s">
@@ -2273,8 +2512,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7" t="n">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="7">
         <v>46059</v>
       </c>
       <c r="B98" s="8" t="s">
@@ -2293,8 +2532,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="n">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="7">
         <v>46059</v>
       </c>
       <c r="B99" s="8" t="s">
@@ -2313,8 +2552,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7" t="n">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="7">
         <v>46059</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -2333,8 +2572,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="n">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="7">
         <v>46059</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -2353,8 +2592,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="n">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="7">
         <v>46059</v>
       </c>
       <c r="B102" s="8" t="s">
@@ -2373,8 +2612,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="n">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="7">
         <v>46059</v>
       </c>
       <c r="B103" s="8" t="s">
@@ -2393,8 +2632,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7" t="n">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="7">
         <v>46059</v>
       </c>
       <c r="B104" s="8" t="s">
@@ -2413,8 +2652,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="n">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="7">
         <v>46059</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -2433,8 +2672,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7" t="n">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="7">
         <v>46059</v>
       </c>
       <c r="B106" s="8" t="s">
@@ -2453,8 +2692,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="n">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="7">
         <v>46059</v>
       </c>
       <c r="B107" s="8" t="s">
@@ -2473,8 +2712,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7" t="n">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="7">
         <v>46059</v>
       </c>
       <c r="B108" s="8" t="s">
@@ -2493,8 +2732,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="n">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="7">
         <v>46059</v>
       </c>
       <c r="B109" s="8" t="s">
@@ -2513,8 +2752,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="n">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="7">
         <v>46059</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -2533,8 +2772,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="n">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="7">
         <v>46059</v>
       </c>
       <c r="B111" s="8" t="s">
@@ -2553,8 +2792,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7" t="n">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="7">
         <v>46059</v>
       </c>
       <c r="B112" s="8" t="s">
@@ -2573,8 +2812,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="n">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="7">
         <v>46059</v>
       </c>
       <c r="B113" s="8" t="s">
@@ -2593,8 +2832,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="n">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="7">
         <v>46059</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -2613,8 +2852,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="10" t="n">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="10">
         <v>46062</v>
       </c>
       <c r="B115" s="11" t="s">
@@ -2633,8 +2872,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="10" t="n">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="10">
         <v>46062</v>
       </c>
       <c r="B116" s="11" t="s">
@@ -2653,8 +2892,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="10" t="n">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="10">
         <v>46063</v>
       </c>
       <c r="B117" s="11" t="s">
@@ -2673,8 +2912,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="10" t="n">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="10">
         <v>46063</v>
       </c>
       <c r="B118" s="11" t="s">
@@ -2693,8 +2932,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="10" t="n">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="10">
         <v>46063</v>
       </c>
       <c r="B119" s="11" t="s">
@@ -2713,8 +2952,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="10" t="n">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="10">
         <v>46063</v>
       </c>
       <c r="B120" s="11" t="s">
@@ -2733,8 +2972,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="10" t="n">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="10">
         <v>46064</v>
       </c>
       <c r="B121" s="11" t="s">
@@ -2753,8 +2992,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="10" t="n">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="10">
         <v>46064</v>
       </c>
       <c r="B122" s="11" t="s">
@@ -2773,8 +3012,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="10" t="n">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="10">
         <v>46064</v>
       </c>
       <c r="B123" s="11" t="s">
@@ -2793,8 +3032,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="10" t="n">
+    <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10">
         <v>46064</v>
       </c>
       <c r="B124" s="11" t="s">
@@ -2813,8 +3052,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="10" t="n">
+    <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10">
         <v>46064</v>
       </c>
       <c r="B125" s="11" t="s">
@@ -2833,8 +3072,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="10" t="n">
+    <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="10">
         <v>46064</v>
       </c>
       <c r="B126" s="11" t="s">
@@ -2853,8 +3092,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="10" t="n">
+    <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="10">
         <v>46064</v>
       </c>
       <c r="B127" s="11" t="s">
@@ -2873,8 +3112,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="10" t="n">
+    <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="10">
         <v>46065</v>
       </c>
       <c r="B128" s="11" t="s">
@@ -2893,8 +3132,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="10" t="n">
+    <row r="129" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="10">
         <v>46065</v>
       </c>
       <c r="B129" s="11" t="s">
@@ -2913,8 +3152,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="10" t="n">
+    <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="10">
         <v>46065</v>
       </c>
       <c r="B130" s="11" t="s">
@@ -2933,8 +3172,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="10" t="n">
+    <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="10">
         <v>46065</v>
       </c>
       <c r="B131" s="11" t="s">
@@ -2953,8 +3192,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="10" t="n">
+    <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="10">
         <v>46066</v>
       </c>
       <c r="B132" s="11" t="s">
@@ -2973,8 +3212,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="10" t="n">
+    <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="10">
         <v>46066</v>
       </c>
       <c r="B133" s="11" t="s">
@@ -2993,8 +3232,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="10" t="n">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="10">
         <v>46069</v>
       </c>
       <c r="B134" s="11" t="s">
@@ -3013,8 +3252,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="10" t="n">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="10">
         <v>46069</v>
       </c>
       <c r="B135" s="11" t="s">
@@ -3033,8 +3272,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="10" t="n">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="10">
         <v>46071</v>
       </c>
       <c r="B136" s="11" t="s">
@@ -3053,8 +3292,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="10" t="n">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="10">
         <v>46071</v>
       </c>
       <c r="B137" s="11" t="s">
@@ -3073,8 +3312,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="10" t="n">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="10">
         <v>46071</v>
       </c>
       <c r="B138" s="11" t="s">
@@ -3093,8 +3332,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="10" t="n">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="10">
         <v>46071</v>
       </c>
       <c r="B139" s="11" t="s">
@@ -3113,8 +3352,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="10" t="n">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="10">
         <v>46071</v>
       </c>
       <c r="B140" s="11" t="s">
@@ -3133,8 +3372,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="10" t="n">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="10">
         <v>46072</v>
       </c>
       <c r="B141" s="11" t="s">
@@ -3153,8 +3392,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="10" t="n">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="10">
         <v>46072</v>
       </c>
       <c r="B142" s="11" t="s">
@@ -3173,8 +3412,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="10" t="n">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="10">
         <v>46072</v>
       </c>
       <c r="B143" s="11" t="s">
@@ -3193,8 +3432,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="10" t="n">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="10">
         <v>46072</v>
       </c>
       <c r="B144" s="11" t="s">
@@ -3213,8 +3452,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="10" t="n">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="10">
         <v>46072</v>
       </c>
       <c r="B145" s="11" t="s">
@@ -3233,8 +3472,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="10" t="n">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="10">
         <v>46072</v>
       </c>
       <c r="B146" s="11" t="s">
@@ -3253,8 +3492,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="10" t="n">
+    <row r="147" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="10">
         <v>46072</v>
       </c>
       <c r="B147" s="11" t="s">
@@ -3273,8 +3512,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="10" t="n">
+    <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="10">
         <v>46072</v>
       </c>
       <c r="B148" s="11" t="s">
@@ -3293,8 +3532,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="10" t="n">
+    <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="10">
         <v>46072</v>
       </c>
       <c r="B149" s="11" t="s">
@@ -3313,8 +3552,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="10" t="n">
+    <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="10">
         <v>46073</v>
       </c>
       <c r="B150" s="11" t="s">
@@ -3333,8 +3572,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="10" t="n">
+    <row r="151" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="10">
         <v>46073</v>
       </c>
       <c r="B151" s="11" t="s">
@@ -3353,8 +3592,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="10" t="n">
+    <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="10">
         <v>46073</v>
       </c>
       <c r="B152" s="11" t="s">
@@ -3373,8 +3612,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="10" t="n">
+    <row r="153" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="10">
         <v>46073</v>
       </c>
       <c r="B153" s="11" t="s">
@@ -3393,8 +3632,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="10" t="n">
+    <row r="154" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="10">
         <v>46073</v>
       </c>
       <c r="B154" s="11" t="s">
@@ -3413,8 +3652,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="10" t="n">
+    <row r="155" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="10">
         <v>46073</v>
       </c>
       <c r="B155" s="11" t="s">
@@ -3433,8 +3672,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="10" t="n">
+    <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="10">
         <v>46073</v>
       </c>
       <c r="B156" s="11" t="s">
@@ -3453,8 +3692,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="10" t="n">
+    <row r="157" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="10">
         <v>46073</v>
       </c>
       <c r="B157" s="11" t="s">
@@ -3473,8 +3712,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="10" t="n">
+    <row r="158" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="10">
         <v>46073</v>
       </c>
       <c r="B158" s="11" t="s">
@@ -3493,8 +3732,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="10" t="n">
+    <row r="159" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="10">
         <v>46073</v>
       </c>
       <c r="B159" s="11" t="s">
@@ -3513,8 +3752,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="10" t="n">
+    <row r="160" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="10">
         <v>46073</v>
       </c>
       <c r="B160" s="11" t="s">
@@ -3533,8 +3772,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="10" t="n">
+    <row r="161" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="10">
         <v>46073</v>
       </c>
       <c r="B161" s="11" t="s">
@@ -3553,8 +3792,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="10" t="n">
+    <row r="162" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="10">
         <v>46073</v>
       </c>
       <c r="B162" s="11" t="s">
@@ -3573,8 +3812,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="10" t="n">
+    <row r="163" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="10">
         <v>46077</v>
       </c>
       <c r="B163" s="11" t="s">
@@ -3593,8 +3832,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="10" t="n">
+    <row r="164" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="10">
         <v>46077</v>
       </c>
       <c r="B164" s="11" t="s">
@@ -3613,8 +3852,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="10" t="n">
+    <row r="165" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="10">
         <v>46077</v>
       </c>
       <c r="B165" s="11" t="s">
@@ -3633,8 +3872,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="10" t="n">
+    <row r="166" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="10">
         <v>46077</v>
       </c>
       <c r="B166" s="11" t="s">
@@ -3653,8 +3892,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="10" t="n">
+    <row r="167" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="10">
         <v>46078</v>
       </c>
       <c r="B167" s="11" t="s">
@@ -3673,8 +3912,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="10" t="n">
+    <row r="168" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="10">
         <v>46078</v>
       </c>
       <c r="B168" s="11" t="s">
@@ -3693,8 +3932,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="10" t="n">
+    <row r="169" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="10">
         <v>46078</v>
       </c>
       <c r="B169" s="11" t="s">
@@ -3713,8 +3952,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="10" t="n">
+    <row r="170" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="10">
         <v>46078</v>
       </c>
       <c r="B170" s="11" t="s">
@@ -3733,8 +3972,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="10" t="n">
+    <row r="171" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="10">
         <v>46079</v>
       </c>
       <c r="B171" s="11" t="s">
@@ -3753,8 +3992,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="10" t="n">
+    <row r="172" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="10">
         <v>46079</v>
       </c>
       <c r="B172" s="11" t="s">
@@ -3773,8 +4012,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="10" t="n">
+    <row r="173" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="10">
         <v>46079</v>
       </c>
       <c r="B173" s="11" t="s">
@@ -3793,8 +4032,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="10" t="n">
+    <row r="174" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="10">
         <v>46079</v>
       </c>
       <c r="B174" s="11" t="s">
@@ -3813,8 +4052,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="10" t="n">
+    <row r="175" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="10">
         <v>46080</v>
       </c>
       <c r="B175" s="11" t="s">
@@ -3833,8 +4072,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="10" t="n">
+    <row r="176" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="10">
         <v>46080</v>
       </c>
       <c r="B176" s="11" t="s">
@@ -3853,8 +4092,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="10" t="n">
+    <row r="177" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="10">
         <v>46080</v>
       </c>
       <c r="B177" s="11" t="s">
@@ -3873,8 +4112,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="10" t="n">
+    <row r="178" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="10">
         <v>46080</v>
       </c>
       <c r="B178" s="11" t="s">
@@ -3893,8 +4132,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="10" t="n">
+    <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="10">
         <v>46083</v>
       </c>
       <c r="B179" s="11" t="s">
@@ -3913,8 +4152,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="10" t="n">
+    <row r="180" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="10">
         <v>46083</v>
       </c>
       <c r="B180" s="11" t="s">
@@ -3933,74 +4172,488 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7"/>
-    </row>
-    <row r="182" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7"/>
-    </row>
-    <row r="183" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7"/>
-    </row>
-    <row r="184" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7"/>
-    </row>
-    <row r="185" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7"/>
-    </row>
-    <row r="186" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7"/>
-    </row>
-    <row r="187" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7"/>
-    </row>
-    <row r="188" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7"/>
-    </row>
-    <row r="189" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7"/>
-    </row>
-    <row r="190" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7"/>
-    </row>
-    <row r="191" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7"/>
-    </row>
-    <row r="192" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7"/>
-    </row>
-    <row r="193" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7"/>
-    </row>
-    <row r="194" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7"/>
-    </row>
-    <row r="195" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7"/>
-    </row>
-    <row r="196" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="7"/>
-    </row>
-    <row r="197" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7"/>
-    </row>
-    <row r="198" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7"/>
-    </row>
-    <row r="199" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="7"/>
-    </row>
-    <row r="200" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="7"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="181" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="7">
+        <v>46108</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="7">
+        <v>46111</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="7">
+        <v>46111</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A201" s="7">
+        <v>46111</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" s="7">
+        <v>46111</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A203" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C5B903-1372-4102-82CC-20730EB938CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB45F94-2B0C-4AFF-9D8D-08388A54736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1755" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matchs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="42">
   <si>
     <t>date</t>
   </si>
@@ -155,6 +155,9 @@
   <si>
     <t>Max</t>
   </si>
+  <si>
+    <t>Théo</t>
+  </si>
 </sst>
 </file>
 
@@ -238,7 +241,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -246,6 +248,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,10 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.25" style="6" customWidth="1"/>
     <col min="2" max="2" width="17.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
@@ -573,3607 +576,3607 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>46048</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>46048</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>46049</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="D4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>46049</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>46049</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="D6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>46049</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>46049</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>46049</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>46049</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>46049</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>46049</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>46049</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>46050</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="B14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>46050</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>46050</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="B16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>46050</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>46050</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="9" t="s">
+      <c r="B18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>46051</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="B19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <v>46052</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="B20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>46052</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <v>46052</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <v>46052</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="B23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="E23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>46052</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>46052</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="B25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <v>46052</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="B26" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>46052</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="9" t="s">
+      <c r="B27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <v>46052</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="B28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="E28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <v>46052</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="B29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="9" t="s">
+      <c r="E29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>46052</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="8" t="s">
+      <c r="B30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="7">
+      <c r="A31" s="6">
         <v>46052</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
+      <c r="A32" s="6">
         <v>46052</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="9" t="s">
+      <c r="D32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
+      <c r="A33" s="6">
         <v>46052</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="B33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
+      <c r="A34" s="6">
         <v>46052</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="C34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="9" t="s">
+      <c r="E34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
+      <c r="A35" s="6">
         <v>46052</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="9" t="s">
+      <c r="E35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <v>46052</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="B36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="9" t="s">
+      <c r="E36" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
+      <c r="A37" s="6">
         <v>46052</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="8" t="s">
+      <c r="B37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="9" t="s">
+      <c r="E37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
+      <c r="A38" s="6">
         <v>46052</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="8" t="s">
+      <c r="B38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="9" t="s">
+      <c r="E38" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
+      <c r="A39" s="6">
         <v>46052</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="8" t="s">
+      <c r="B39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
+      <c r="A40" s="6">
         <v>46052</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="8" t="s">
+      <c r="C40" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="7">
+      <c r="A41" s="6">
         <v>46052</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="9" t="s">
+      <c r="C41" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="7">
+      <c r="A42" s="6">
         <v>46055</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="7">
+      <c r="A43" s="6">
         <v>46055</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="8" t="s">
+      <c r="B43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
+      <c r="E43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
+      <c r="A44" s="6">
         <v>46055</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="8" t="s">
+      <c r="C44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
+      <c r="A45" s="6">
         <v>46056</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" s="8" t="s">
+      <c r="B45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="7">
+      <c r="A46" s="6">
         <v>46056</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="8" t="s">
+      <c r="B46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="9" t="s">
+      <c r="E46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="7">
+      <c r="A47" s="6">
         <v>46056</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="8" t="s">
+      <c r="C47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="7">
+      <c r="A48" s="6">
         <v>46057</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="7">
+      <c r="A49" s="6">
         <v>46057</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="8" t="s">
+      <c r="B49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="7">
+      <c r="A50" s="6">
         <v>46057</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="8" t="s">
+      <c r="C50" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="9" t="s">
+      <c r="E50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="7">
+      <c r="A51" s="6">
         <v>46057</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="B51" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="7">
+      <c r="A52" s="6">
         <v>46057</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="8" t="s">
+      <c r="B52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" s="9" t="s">
+      <c r="E52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
+      <c r="A53" s="6">
         <v>46057</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E53" s="8" t="s">
+      <c r="B53" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="7">
+      <c r="A54" s="6">
         <v>46057</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="9" t="s">
+      <c r="C54" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="7">
+      <c r="A55" s="6">
         <v>46058</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="8" t="s">
+      <c r="C55" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="7">
+      <c r="A56" s="6">
         <v>46058</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="8" t="s">
+      <c r="D56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="7">
+      <c r="A57" s="6">
         <v>46058</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="8" t="s">
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="7">
+      <c r="A58" s="6">
         <v>46058</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58" s="8" t="s">
+      <c r="D58" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="7">
+      <c r="A59" s="6">
         <v>46058</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="8" t="s">
+      <c r="D59" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="7">
+      <c r="A60" s="6">
         <v>46058</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="9" t="s">
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="7">
+      <c r="A61" s="6">
         <v>46058</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F61" s="9" t="s">
+      <c r="C61" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="7">
+      <c r="A62" s="6">
         <v>46058</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D62" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9" t="s">
+      <c r="D62" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="7">
+      <c r="A63" s="6">
         <v>46058</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" s="9" t="s">
+      <c r="D63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="7">
+      <c r="A64" s="6">
         <v>46058</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="8" t="s">
+      <c r="B64" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
+      <c r="E64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="7">
+      <c r="A65" s="6">
         <v>46058</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="B65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="7">
+      <c r="A66" s="6">
         <v>46058</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F66" s="9" t="s">
+      <c r="C66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="7">
+      <c r="A67" s="6">
         <v>46058</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F67" s="9" t="s">
+      <c r="B67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="7">
+      <c r="A68" s="6">
         <v>46058</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="9" t="s">
+      <c r="B68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="7">
+      <c r="A69" s="6">
         <v>46058</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" s="9" t="s">
+      <c r="B69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="7">
+      <c r="A70" s="6">
         <v>46058</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F70" s="9" t="s">
+      <c r="B70" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="7">
+      <c r="A71" s="6">
         <v>46059</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="B71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="8" t="s">
+      <c r="D71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F71" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="7">
+      <c r="A72" s="6">
         <v>46059</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="7">
+      <c r="A73" s="6">
         <v>46059</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C73" s="8" t="s">
+      <c r="B73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D73" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
+      <c r="D73" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="7">
+      <c r="A74" s="6">
         <v>46059</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="9" t="s">
+      <c r="B74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="7">
+      <c r="A75" s="6">
         <v>46059</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
+      <c r="B75" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="7">
+      <c r="A76" s="6">
         <v>46059</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="9" t="s">
+      <c r="B76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="7">
+      <c r="A77" s="6">
         <v>46059</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F77" s="9" t="s">
+      <c r="B77" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="7">
+      <c r="A78" s="6">
         <v>46059</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
+      <c r="B78" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="7">
+      <c r="A79" s="6">
         <v>46059</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" s="9" t="s">
+      <c r="B79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="7">
+      <c r="A80" s="6">
         <v>46059</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F80" s="9" t="s">
+      <c r="B80" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="7">
+      <c r="A81" s="6">
         <v>46059</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" s="9" t="s">
+      <c r="C81" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="7">
+      <c r="A82" s="6">
         <v>46059</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="9" t="s">
+      <c r="C82" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="7">
+      <c r="A83" s="6">
         <v>46059</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="8" t="s">
+      <c r="C83" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E83" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83" s="9" t="s">
+      <c r="E83" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="7">
+      <c r="A84" s="6">
         <v>46059</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="8" t="s">
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E84" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" s="9" t="s">
+      <c r="E84" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="7">
+      <c r="A85" s="6">
         <v>46059</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F85" s="9" t="s">
+      <c r="D85" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="7">
+      <c r="A86" s="6">
         <v>46059</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="9" t="s">
+      <c r="B86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="7">
+      <c r="A87" s="6">
         <v>46059</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E87" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F87" s="9" t="s">
+      <c r="E87" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="7">
+      <c r="A88" s="6">
         <v>46059</v>
       </c>
-      <c r="B88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F88" s="9" t="s">
+      <c r="B88" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="7">
+      <c r="A89" s="6">
         <v>46059</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="9" t="s">
+      <c r="B89" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="7">
+      <c r="A90" s="6">
         <v>46059</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="8" t="s">
+      <c r="B90" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="F90" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="7">
+      <c r="A91" s="6">
         <v>46059</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F91" s="9" t="s">
+      <c r="B91" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="7">
+      <c r="A92" s="6">
         <v>46059</v>
       </c>
-      <c r="B92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" s="9" t="s">
+      <c r="B92" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F92" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="7">
+      <c r="A93" s="6">
         <v>46059</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F93" s="9" t="s">
+      <c r="B93" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="7">
+      <c r="A94" s="6">
         <v>46059</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" s="9" t="s">
+      <c r="B94" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="7">
+      <c r="A95" s="6">
         <v>46059</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" s="9" t="s">
+      <c r="B95" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F95" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="7">
+      <c r="A96" s="6">
         <v>46059</v>
       </c>
-      <c r="B96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" s="9" t="s">
+      <c r="B96" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" s="7">
+      <c r="A97" s="6">
         <v>46059</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" s="9" t="s">
+      <c r="B97" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F97" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="7">
+      <c r="A98" s="6">
         <v>46059</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" s="9" t="s">
+      <c r="B98" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="7">
+      <c r="A99" s="6">
         <v>46059</v>
       </c>
-      <c r="B99" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F99" s="9" t="s">
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="7">
+      <c r="A100" s="6">
         <v>46059</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="9" t="s">
+      <c r="B100" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="7">
+      <c r="A101" s="6">
         <v>46059</v>
       </c>
-      <c r="B101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F101" s="9" t="s">
+      <c r="B101" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="7">
+      <c r="A102" s="6">
         <v>46059</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" s="9" t="s">
+      <c r="B102" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" s="7">
+      <c r="A103" s="6">
         <v>46059</v>
       </c>
-      <c r="B103" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F103" s="9" t="s">
+      <c r="B103" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" s="7">
+      <c r="A104" s="6">
         <v>46059</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
+      <c r="B104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="7">
+      <c r="A105" s="6">
         <v>46059</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" s="9" t="s">
+      <c r="B105" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="7">
+      <c r="A106" s="6">
         <v>46059</v>
       </c>
-      <c r="B106" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" s="9" t="s">
+      <c r="B106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="7">
+      <c r="A107" s="6">
         <v>46059</v>
       </c>
-      <c r="B107" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" s="9" t="s">
+      <c r="B107" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="7">
+      <c r="A108" s="6">
         <v>46059</v>
       </c>
-      <c r="B108" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F108" s="9" t="s">
+      <c r="B108" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" s="7">
+      <c r="A109" s="6">
         <v>46059</v>
       </c>
-      <c r="B109" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="9" t="s">
+      <c r="B109" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="7">
+      <c r="A110" s="6">
         <v>46059</v>
       </c>
-      <c r="B110" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F110" s="9" t="s">
+      <c r="B110" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" s="7">
+      <c r="A111" s="6">
         <v>46059</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" s="9" t="s">
+      <c r="B111" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="7">
+      <c r="A112" s="6">
         <v>46059</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" s="9" t="s">
+      <c r="B112" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F112" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="7">
+      <c r="A113" s="6">
         <v>46059</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F113" s="9" t="s">
+      <c r="B113" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F113" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="7">
+      <c r="A114" s="6">
         <v>46059</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="9" t="s">
+      <c r="B114" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="10">
+      <c r="A115" s="9">
         <v>46062</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F115" s="11" t="s">
+      <c r="F115" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="10">
+      <c r="A116" s="9">
         <v>46062</v>
       </c>
-      <c r="B116" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" s="11" t="s">
+      <c r="B116" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D116" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" s="11" t="s">
+      <c r="D116" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="10">
+      <c r="A117" s="9">
         <v>46063</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D117" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F117" s="11" t="s">
+      <c r="F117" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="10">
+      <c r="A118" s="9">
         <v>46063</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D118" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="F118" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="10">
+      <c r="A119" s="9">
         <v>46063</v>
       </c>
-      <c r="B119" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="11" t="s">
+      <c r="B119" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F119" s="11" t="s">
+      <c r="F119" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="10">
+      <c r="A120" s="9">
         <v>46063</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D120" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F120" s="11" t="s">
+      <c r="F120" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="10">
+      <c r="A121" s="9">
         <v>46064</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D121" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" s="11" t="s">
+      <c r="D121" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F121" s="11" t="s">
+      <c r="F121" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="10">
+      <c r="A122" s="9">
         <v>46064</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D122" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E122" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" s="11" t="s">
+      <c r="E122" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="10">
+      <c r="A123" s="9">
         <v>46064</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D123" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E123" s="11" t="s">
+      <c r="D123" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F123" s="11" t="s">
+      <c r="F123" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="10">
+      <c r="A124" s="9">
         <v>46064</v>
       </c>
-      <c r="B124" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="11" t="s">
+      <c r="B124" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E124" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F124" s="11" t="s">
+      <c r="F124" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="10">
+      <c r="A125" s="9">
         <v>46064</v>
       </c>
-      <c r="B125" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C125" s="11" t="s">
+      <c r="B125" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="11" t="s">
+      <c r="D125" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="10">
+      <c r="A126" s="9">
         <v>46064</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C126" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F126" s="11" t="s">
+      <c r="D126" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="10">
+      <c r="A127" s="9">
         <v>46064</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C127" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" s="11" t="s">
+      <c r="C127" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="10">
+      <c r="A128" s="9">
         <v>46065</v>
       </c>
-      <c r="B128" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="11" t="s">
+      <c r="B128" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E128" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" s="11" t="s">
+      <c r="E128" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="10">
+      <c r="A129" s="9">
         <v>46065</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C129" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D129" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F129" s="11" t="s">
+      <c r="F129" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="10">
+      <c r="A130" s="9">
         <v>46065</v>
       </c>
-      <c r="B130" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130" s="11" t="s">
+      <c r="B130" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="F130" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="10">
+      <c r="A131" s="9">
         <v>46065</v>
       </c>
-      <c r="B131" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="11" t="s">
+      <c r="B131" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E131" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F131" s="11" t="s">
+      <c r="F131" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="10">
+      <c r="A132" s="9">
         <v>46066</v>
       </c>
-      <c r="B132" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" s="11" t="s">
+      <c r="B132" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D132" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F132" s="11" t="s">
+      <c r="F132" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="10">
+      <c r="A133" s="9">
         <v>46066</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D133" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="11" t="s">
+      <c r="D133" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F133" s="11" t="s">
+      <c r="F133" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" s="10">
+      <c r="A134" s="9">
         <v>46069</v>
       </c>
-      <c r="B134" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" s="11" t="s">
+      <c r="B134" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D134" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E134" s="11" t="s">
+      <c r="D134" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F134" s="11" t="s">
+      <c r="F134" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" s="10">
+      <c r="A135" s="9">
         <v>46069</v>
       </c>
-      <c r="B135" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135" s="11" t="s">
+      <c r="B135" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E135" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F135" s="11" t="s">
+      <c r="F135" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136" s="10">
+      <c r="A136" s="9">
         <v>46071</v>
       </c>
-      <c r="B136" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C136" s="11" t="s">
+      <c r="B136" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D136" s="11" t="s">
+      <c r="D136" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E136" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="11" t="s">
+      <c r="E136" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" s="10">
+      <c r="A137" s="9">
         <v>46071</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" s="11" t="s">
+      <c r="B137" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D137" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E137" s="11" t="s">
+      <c r="D137" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F137" s="11" t="s">
+      <c r="F137" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138" s="10">
+      <c r="A138" s="9">
         <v>46071</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C138" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="11" t="s">
+      <c r="C138" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F138" s="11" t="s">
+      <c r="F138" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139" s="10">
+      <c r="A139" s="9">
         <v>46071</v>
       </c>
-      <c r="B139" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="11" t="s">
+      <c r="B139" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="E139" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F139" s="11" t="s">
+      <c r="F139" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" s="10">
+      <c r="A140" s="9">
         <v>46071</v>
       </c>
-      <c r="B140" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" s="11" t="s">
+      <c r="B140" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D140" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E140" s="11" t="s">
+      <c r="D140" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F140" s="11" t="s">
+      <c r="F140" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141" s="10">
+      <c r="A141" s="9">
         <v>46072</v>
       </c>
-      <c r="B141" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" s="11" t="s">
+      <c r="B141" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F141" s="11" t="s">
+      <c r="F141" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" s="10">
+      <c r="A142" s="9">
         <v>46072</v>
       </c>
-      <c r="B142" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="11" t="s">
+      <c r="B142" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D142" s="11" t="s">
+      <c r="D142" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="E142" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F142" s="11" t="s">
+      <c r="F142" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A143" s="10">
+      <c r="A143" s="9">
         <v>46072</v>
       </c>
-      <c r="B143" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" s="11" t="s">
+      <c r="B143" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" s="11" t="s">
+      <c r="D143" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F143" s="11" t="s">
+      <c r="F143" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" s="10">
+      <c r="A144" s="9">
         <v>46072</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C144" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D144" s="11" t="s">
+      <c r="C144" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E144" s="11" t="s">
+      <c r="E144" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F144" s="11" t="s">
+      <c r="F144" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145" s="10">
+      <c r="A145" s="9">
         <v>46072</v>
       </c>
-      <c r="B145" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D145" s="11" t="s">
+      <c r="B145" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E145" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F145" s="11" t="s">
+      <c r="E145" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F145" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A146" s="10">
+      <c r="A146" s="9">
         <v>46072</v>
       </c>
-      <c r="B146" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D146" s="11" t="s">
+      <c r="B146" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F146" s="11" t="s">
+      <c r="E146" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F146" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="10">
+      <c r="A147" s="9">
         <v>46072</v>
       </c>
-      <c r="B147" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D147" s="11" t="s">
+      <c r="B147" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E147" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="11" t="s">
+      <c r="E147" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="10">
+      <c r="A148" s="9">
         <v>46072</v>
       </c>
-      <c r="B148" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E148" s="11" t="s">
+      <c r="B148" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F148" s="11" t="s">
+      <c r="F148" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="10">
+      <c r="A149" s="9">
         <v>46072</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F149" s="11" t="s">
+      <c r="C149" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="10">
+      <c r="A150" s="9">
         <v>46073</v>
       </c>
-      <c r="B150" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E150" s="11" t="s">
+      <c r="B150" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F150" s="11" t="s">
+      <c r="F150" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="10">
+      <c r="A151" s="9">
         <v>46073</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D151" s="11" t="s">
+      <c r="D151" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F151" s="11" t="s">
+      <c r="F151" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="10">
+      <c r="A152" s="9">
         <v>46073</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C152" s="11" t="s">
+      <c r="C152" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="D152" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E152" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F152" s="11" t="s">
+      <c r="E152" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F152" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="10">
+      <c r="A153" s="9">
         <v>46073</v>
       </c>
-      <c r="B153" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D153" s="11" t="s">
+      <c r="B153" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E153" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F153" s="11" t="s">
+      <c r="E153" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="10">
+      <c r="A154" s="9">
         <v>46073</v>
       </c>
-      <c r="B154" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C154" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154" s="11" t="s">
+      <c r="B154" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E154" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F154" s="11" t="s">
+      <c r="F154" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="10">
+      <c r="A155" s="9">
         <v>46073</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="C155" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D155" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E155" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F155" s="11" t="s">
+      <c r="D155" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F155" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="10">
+      <c r="A156" s="9">
         <v>46073</v>
       </c>
-      <c r="B156" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156" s="11" t="s">
+      <c r="B156" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F156" s="11" t="s">
+      <c r="F156" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="10">
+      <c r="A157" s="9">
         <v>46073</v>
       </c>
-      <c r="B157" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="11" t="s">
+      <c r="B157" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F157" s="11" t="s">
+      <c r="F157" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="10">
+      <c r="A158" s="9">
         <v>46073</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E158" s="11" t="s">
+      <c r="C158" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F158" s="11" t="s">
+      <c r="F158" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="10">
+      <c r="A159" s="9">
         <v>46073</v>
       </c>
-      <c r="B159" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="11" t="s">
+      <c r="B159" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="10">
+      <c r="A160" s="9">
         <v>46073</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C160" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" s="11" t="s">
+      <c r="C160" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="10">
+      <c r="A161" s="9">
         <v>46073</v>
       </c>
-      <c r="B161" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E161" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F161" s="11" t="s">
+      <c r="B161" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F161" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="10">
+      <c r="A162" s="9">
         <v>46073</v>
       </c>
-      <c r="B162" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F162" s="11" t="s">
+      <c r="B162" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="10">
+      <c r="A163" s="9">
         <v>46077</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C163" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D163" s="11" t="s">
+      <c r="C163" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E163" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="11" t="s">
+      <c r="E163" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="10">
+      <c r="A164" s="9">
         <v>46077</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C164" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164" s="11" t="s">
+      <c r="C164" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E164" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F164" s="11" t="s">
+      <c r="E164" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="10">
+      <c r="A165" s="9">
         <v>46077</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C165" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="11" t="s">
+      <c r="C165" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E165" s="11" t="s">
+      <c r="E165" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F165" s="11" t="s">
+      <c r="F165" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="10">
+      <c r="A166" s="9">
         <v>46077</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C166" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E166" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F166" s="11" t="s">
+      <c r="C166" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="10">
+      <c r="A167" s="9">
         <v>46078</v>
       </c>
-      <c r="B167" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" s="11" t="s">
+      <c r="B167" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D167" s="11" t="s">
+      <c r="D167" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E167" s="11" t="s">
+      <c r="E167" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F167" s="11" t="s">
+      <c r="F167" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="10">
+      <c r="A168" s="9">
         <v>46078</v>
       </c>
-      <c r="B168" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C168" s="11" t="s">
+      <c r="B168" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D168" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E168" s="11" t="s">
+      <c r="D168" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F168" s="11" t="s">
+      <c r="F168" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="10">
+      <c r="A169" s="9">
         <v>46078</v>
       </c>
-      <c r="B169" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C169" s="11" t="s">
+      <c r="B169" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D169" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E169" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="11" t="s">
+      <c r="D169" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="10">
+      <c r="A170" s="9">
         <v>46078</v>
       </c>
-      <c r="B170" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" s="11" t="s">
+      <c r="B170" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F170" s="11" t="s">
+      <c r="F170" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="10">
+      <c r="A171" s="9">
         <v>46079</v>
       </c>
-      <c r="B171" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C171" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D171" s="11" t="s">
+      <c r="B171" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E171" s="11" t="s">
+      <c r="E171" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F171" s="11" t="s">
+      <c r="F171" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="10">
+      <c r="A172" s="9">
         <v>46079</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D172" s="11" t="s">
+      <c r="D172" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E172" s="11" t="s">
+      <c r="E172" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F172" s="11" t="s">
+      <c r="F172" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="10">
+      <c r="A173" s="9">
         <v>46079</v>
       </c>
-      <c r="B173" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E173" s="11" t="s">
+      <c r="B173" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F173" s="11" t="s">
+      <c r="F173" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="10">
+      <c r="A174" s="9">
         <v>46079</v>
       </c>
-      <c r="B174" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C174" s="11" t="s">
+      <c r="B174" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D174" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E174" s="11" t="s">
+      <c r="D174" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F174" s="11" t="s">
+      <c r="F174" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="10">
+      <c r="A175" s="9">
         <v>46080</v>
       </c>
-      <c r="B175" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D175" s="11" t="s">
+      <c r="B175" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D175" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E175" s="11" t="s">
+      <c r="E175" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F175" s="11" t="s">
+      <c r="F175" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="10">
+      <c r="A176" s="9">
         <v>46080</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="C176" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D176" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E176" s="11" t="s">
+      <c r="D176" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F176" s="11" t="s">
+      <c r="F176" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="10">
+      <c r="A177" s="9">
         <v>46080</v>
       </c>
-      <c r="B177" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" s="11" t="s">
+      <c r="B177" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="D177" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E177" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="11" t="s">
+      <c r="E177" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="10">
+      <c r="A178" s="9">
         <v>46080</v>
       </c>
-      <c r="B178" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C178" s="11" t="s">
+      <c r="B178" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D178" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E178" s="11" t="s">
+      <c r="D178" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F178" s="11" t="s">
+      <c r="F178" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="10">
+      <c r="A179" s="9">
         <v>46083</v>
       </c>
-      <c r="B179" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C179" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D179" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E179" s="11" t="s">
+      <c r="B179" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F179" s="11" t="s">
+      <c r="F179" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="10">
+      <c r="A180" s="9">
         <v>46083</v>
       </c>
-      <c r="B180" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C180" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D180" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E180" s="11" t="s">
+      <c r="B180" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E180" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F180" s="11" t="s">
+      <c r="F180" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="7">
+      <c r="A181" s="6">
         <v>46084</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -4193,7 +4196,7 @@
       </c>
     </row>
     <row r="182" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="7">
+      <c r="A182" s="6">
         <v>46084</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -4213,7 +4216,7 @@
       </c>
     </row>
     <row r="183" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="7">
+      <c r="A183" s="6">
         <v>46084</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -4233,7 +4236,7 @@
       </c>
     </row>
     <row r="184" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="7">
+      <c r="A184" s="6">
         <v>46084</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -4253,7 +4256,7 @@
       </c>
     </row>
     <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="7">
+      <c r="A185" s="6">
         <v>46085</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -4273,7 +4276,7 @@
       </c>
     </row>
     <row r="186" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="7">
+      <c r="A186" s="6">
         <v>46085</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -4293,7 +4296,7 @@
       </c>
     </row>
     <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="7">
+      <c r="A187" s="6">
         <v>46106</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -4313,7 +4316,7 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="7">
+      <c r="A188" s="6">
         <v>46106</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -4333,7 +4336,7 @@
       </c>
     </row>
     <row r="189" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="7">
+      <c r="A189" s="6">
         <v>46106</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -4353,7 +4356,7 @@
       </c>
     </row>
     <row r="190" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="7">
+      <c r="A190" s="6">
         <v>46107</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -4373,7 +4376,7 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="7">
+      <c r="A191" s="6">
         <v>46107</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -4393,7 +4396,7 @@
       </c>
     </row>
     <row r="192" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="7">
+      <c r="A192" s="6">
         <v>46108</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -4413,7 +4416,7 @@
       </c>
     </row>
     <row r="193" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="7">
+      <c r="A193" s="6">
         <v>46108</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -4433,7 +4436,7 @@
       </c>
     </row>
     <row r="194" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="7">
+      <c r="A194" s="6">
         <v>46108</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -4453,7 +4456,7 @@
       </c>
     </row>
     <row r="195" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="7">
+      <c r="A195" s="6">
         <v>46108</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -4473,7 +4476,7 @@
       </c>
     </row>
     <row r="196" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="7">
+      <c r="A196" s="6">
         <v>46108</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -4493,7 +4496,7 @@
       </c>
     </row>
     <row r="197" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="7">
+      <c r="A197" s="6">
         <v>46108</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -4513,7 +4516,7 @@
       </c>
     </row>
     <row r="198" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="7">
+      <c r="A198" s="6">
         <v>46108</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -4533,7 +4536,7 @@
       </c>
     </row>
     <row r="199" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="7">
+      <c r="A199" s="6">
         <v>46111</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -4553,7 +4556,7 @@
       </c>
     </row>
     <row r="200" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="7">
+      <c r="A200" s="6">
         <v>46111</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -4573,7 +4576,7 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A201" s="7">
+      <c r="A201" s="6">
         <v>46111</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -4593,7 +4596,7 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A202" s="7">
+      <c r="A202" s="6">
         <v>46111</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -4613,7 +4616,7 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A203" s="7">
+      <c r="A203" s="6">
         <v>46112</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -4633,7 +4636,7 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A204" s="7">
+      <c r="A204" s="6">
         <v>46112</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -4649,6 +4652,86 @@
         <v>7</v>
       </c>
       <c r="F204" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A206" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A207" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A208" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB45F94-2B0C-4AFF-9D8D-08388A54736D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2049B4D8-AF4D-46AD-9275-E38C43619895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1755" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matchs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">matchs!$A$1:$G$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">matchs!$A$1:$F$116</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="41">
   <si>
     <t>date</t>
   </si>
@@ -126,9 +127,6 @@
     <t>JulieB</t>
   </si>
   <si>
-    <t>TheoM</t>
-  </si>
-  <si>
     <t>Mountassira</t>
   </si>
   <si>
@@ -156,7 +154,7 @@
     <t>Max</t>
   </si>
   <si>
-    <t>Théo</t>
+    <t>ThéoM</t>
   </si>
 </sst>
 </file>
@@ -563,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.25" style="6" customWidth="1"/>
@@ -1526,10 +1524,10 @@
         <v>30</v>
       </c>
       <c r="D48" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>10</v>
@@ -1566,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>20</v>
@@ -1586,7 +1584,7 @@
         <v>7</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>21</v>
@@ -1606,7 +1604,7 @@
         <v>14</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>20</v>
@@ -1689,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>10</v>
@@ -1709,7 +1707,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>11</v>
@@ -1723,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>16</v>
@@ -1749,7 +1747,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>11</v>
@@ -1803,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>9</v>
@@ -1983,13 +1981,13 @@
         <v>13</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>10</v>
@@ -2000,10 +1998,10 @@
         <v>46059</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>26</v>
@@ -2023,7 +2021,7 @@
         <v>14</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>7</v>
@@ -2869,7 +2867,7 @@
         <v>29</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>11</v>
@@ -2883,7 +2881,7 @@
         <v>20</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>13</v>
@@ -2900,10 +2898,10 @@
         <v>46063</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>26</v>
@@ -2923,13 +2921,13 @@
         <v>26</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F118" s="10" t="s">
         <v>11</v>
@@ -2946,7 +2944,7 @@
         <v>13</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>18</v>
@@ -2969,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F120" s="10" t="s">
         <v>10</v>
@@ -2989,7 +2987,7 @@
         <v>14</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>11</v>
@@ -3000,7 +2998,7 @@
         <v>46064</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>15</v>
@@ -3049,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>11</v>
@@ -3080,7 +3078,7 @@
         <v>46064</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>8</v>
@@ -3126,7 +3124,7 @@
         <v>30</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>7</v>
@@ -3149,7 +3147,7 @@
         <v>18</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>10</v>
@@ -3169,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F130" s="10" t="s">
         <v>11</v>
@@ -3189,7 +3187,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>11</v>
@@ -3206,10 +3204,10 @@
         <v>29</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>11</v>
@@ -3223,13 +3221,13 @@
         <v>19</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>10</v>
@@ -3266,7 +3264,7 @@
         <v>7</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>18</v>
@@ -3329,7 +3327,7 @@
         <v>18</v>
       </c>
       <c r="E138" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F138" s="10" t="s">
         <v>10</v>
@@ -3446,7 +3444,7 @@
         <v>14</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E144" s="10" t="s">
         <v>29</v>
@@ -3486,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E146" s="10" t="s">
         <v>7</v>
@@ -3589,7 +3587,7 @@
         <v>21</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>10</v>
@@ -3600,7 +3598,7 @@
         <v>46073</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>8</v>
@@ -3646,7 +3644,7 @@
         <v>7</v>
       </c>
       <c r="D154" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E154" s="10" t="s">
         <v>8</v>
@@ -3660,10 +3658,10 @@
         <v>46073</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>13</v>
@@ -3840,7 +3838,7 @@
         <v>46077</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>7</v>
@@ -3909,7 +3907,7 @@
         <v>12</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>10</v>
@@ -3923,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D168" s="10" t="s">
         <v>7</v>
@@ -3943,7 +3941,7 @@
         <v>14</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>7</v>
@@ -3969,7 +3967,7 @@
         <v>14</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F170" s="10" t="s">
         <v>11</v>
@@ -4000,13 +3998,13 @@
         <v>46079</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D172" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E172" s="10" t="s">
         <v>29</v>
@@ -4049,7 +4047,7 @@
         <v>16</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F174" s="10" t="s">
         <v>10</v>
@@ -4080,10 +4078,10 @@
         <v>46080</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>7</v>
@@ -4103,7 +4101,7 @@
         <v>16</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>21</v>
@@ -4149,7 +4147,7 @@
         <v>14</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>11</v>
@@ -4169,7 +4167,7 @@
         <v>20</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>11</v>
@@ -4206,7 +4204,7 @@
         <v>17</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>16</v>
@@ -4223,7 +4221,7 @@
         <v>20</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>21</v>
@@ -4246,10 +4244,10 @@
         <v>13</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>11</v>
@@ -4269,7 +4267,7 @@
         <v>20</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>11</v>
@@ -4283,7 +4281,7 @@
         <v>20</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>7</v>
@@ -4303,7 +4301,7 @@
         <v>18</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>8</v>
@@ -4326,7 +4324,7 @@
         <v>21</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
@@ -4369,7 +4367,7 @@
         <v>8</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>11</v>
@@ -4449,7 +4447,7 @@
         <v>21</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>10</v>
@@ -4489,7 +4487,7 @@
         <v>21</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>11</v>
@@ -4540,10 +4538,10 @@
         <v>46111</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>30</v>
@@ -4569,7 +4567,7 @@
         <v>21</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>11</v>
@@ -4583,7 +4581,7 @@
         <v>9</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>21</v>
@@ -4606,7 +4604,7 @@
         <v>20</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>7</v>
@@ -4680,10 +4678,10 @@
         <v>46113</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>30</v>
@@ -4720,7 +4718,7 @@
         <v>46113</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>9</v>
@@ -4733,6 +4731,206 @@
       </c>
       <c r="F208" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A209" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" s="6">
+        <v>46115</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" s="6">
+        <v>46115</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A217" s="6">
+        <v>46115</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" s="6">
+        <v>46115</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CD0106-B3A3-4D64-B2CB-F146DBF8AA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="false" showVerticalScroll="false" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="matchs" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="matchs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">matchs!$A$1:$F$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">matchs!$A$1:$F$116</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,176 +31,160 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="47">
   <si>
-    <t xml:space="preserve">date</t>
+    <t>date</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge_p1</t>
+    <t>rouge_p1</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge_p2</t>
+    <t>rouge_p2</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu_p1</t>
+    <t>bleu_p1</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu_p2</t>
+    <t>bleu_p2</t>
   </si>
   <si>
-    <t xml:space="preserve">vainqueur</t>
+    <t>vainqueur</t>
   </si>
   <si>
-    <t xml:space="preserve">NathV</t>
+    <t>NathV</t>
   </si>
   <si>
-    <t xml:space="preserve">Lily</t>
+    <t>Lily</t>
   </si>
   <si>
-    <t xml:space="preserve">Roland</t>
+    <t>Roland</t>
   </si>
   <si>
-    <t xml:space="preserve">Rémi</t>
+    <t>Rémi</t>
   </si>
   <si>
-    <t xml:space="preserve">bleu</t>
+    <t>bleu</t>
   </si>
   <si>
-    <t xml:space="preserve">rouge</t>
+    <t>rouge</t>
   </si>
   <si>
-    <t xml:space="preserve">ManonV</t>
+    <t>ManonV</t>
   </si>
   <si>
-    <t xml:space="preserve">Lilou</t>
+    <t>Lilou</t>
   </si>
   <si>
-    <t xml:space="preserve">Paul</t>
+    <t>Paul</t>
   </si>
   <si>
-    <t xml:space="preserve">Anne-Laure P</t>
+    <t>Anne-Laure P</t>
   </si>
   <si>
-    <t xml:space="preserve">Raphaël</t>
+    <t>Raphaël</t>
   </si>
   <si>
-    <t xml:space="preserve">Benoit</t>
+    <t>Benoit</t>
   </si>
   <si>
-    <t xml:space="preserve">Julia</t>
+    <t>Julia</t>
   </si>
   <si>
-    <t xml:space="preserve">Armelle</t>
+    <t>Armelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Jules</t>
+    <t>Jules</t>
   </si>
   <si>
-    <t xml:space="preserve">BenjaminC</t>
+    <t>BenjaminC</t>
   </si>
   <si>
-    <t xml:space="preserve">Jasmine</t>
+    <t>Jasmine</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanguy</t>
+    <t>Tanguy</t>
   </si>
   <si>
-    <t xml:space="preserve">Marguerite</t>
+    <t>Marguerite</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom</t>
+    <t>Tom</t>
   </si>
   <si>
-    <t xml:space="preserve">LaureS</t>
+    <t>LaureS</t>
   </si>
   <si>
-    <t xml:space="preserve">Sabine</t>
+    <t>Sabine</t>
   </si>
   <si>
-    <t xml:space="preserve">SimonB</t>
+    <t>SimonB</t>
   </si>
   <si>
-    <t xml:space="preserve">Loïc</t>
+    <t>Loïc</t>
   </si>
   <si>
-    <t xml:space="preserve">JulieB</t>
+    <t>JulieB</t>
   </si>
   <si>
-    <t xml:space="preserve">ThéoM</t>
+    <t>ThéoM</t>
   </si>
   <si>
-    <t xml:space="preserve">Mountassira</t>
+    <t>Mountassira</t>
   </si>
   <si>
-    <t xml:space="preserve">EmmanuelP</t>
+    <t>EmmanuelP</t>
   </si>
   <si>
-    <t xml:space="preserve">VincentD</t>
+    <t>VincentD</t>
   </si>
   <si>
-    <t xml:space="preserve">BenjaminZ</t>
+    <t>BenjaminZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximilien</t>
+    <t>Maximilien</t>
   </si>
   <si>
-    <t xml:space="preserve">Anna</t>
+    <t>Anna</t>
   </si>
   <si>
-    <t xml:space="preserve">PhilippeA</t>
+    <t>PhilippeA</t>
   </si>
   <si>
-    <t xml:space="preserve">DenisB</t>
+    <t>DenisB</t>
   </si>
   <si>
-    <t xml:space="preserve">Max</t>
+    <t>Max</t>
   </si>
   <si>
-    <t xml:space="preserve">Nicolas</t>
+    <t>Nicolas</t>
   </si>
   <si>
-    <t xml:space="preserve">Solal</t>
+    <t>Solal</t>
   </si>
   <si>
-    <t xml:space="preserve">SayaCopainManon</t>
+    <t>SayaCopainManon</t>
   </si>
   <si>
-    <t xml:space="preserve">JulienM</t>
+    <t>JulienM</t>
   </si>
   <si>
-    <t xml:space="preserve">Rouge</t>
+    <t>Rouge</t>
+  </si>
+  <si>
+    <t>Aude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="18"/>
@@ -202,7 +194,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -219,187 +211,125 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -431,7 +361,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -455,7 +385,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -515,32 +445,31 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F302"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="23.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G338"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="14.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="10.88"/>
+    <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -560,8 +489,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>46048</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -580,8 +509,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>46048</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -600,8 +529,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>46049</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -620,8 +549,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>46049</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -640,8 +569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
         <v>46049</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -660,8 +589,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
         <v>46049</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -680,8 +609,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>46049</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -700,8 +629,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>46049</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -720,8 +649,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
         <v>46049</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -740,8 +669,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
         <v>46049</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -760,8 +689,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
         <v>46049</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -780,8 +709,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
         <v>46049</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -800,8 +729,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
         <v>46050</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -820,8 +749,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
         <v>46050</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -840,8 +769,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
         <v>46050</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -860,8 +789,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
         <v>46050</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -880,8 +809,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
         <v>46050</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -900,8 +829,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
         <v>46051</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -920,8 +849,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
         <v>46052</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -940,8 +869,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
         <v>46052</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -960,8 +889,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
         <v>46052</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -980,8 +909,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
         <v>46052</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -1000,8 +929,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
         <v>46052</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1020,8 +949,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
         <v>46052</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -1040,8 +969,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
         <v>46052</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -1060,8 +989,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
         <v>46052</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -1080,8 +1009,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
         <v>46052</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1100,8 +1029,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
         <v>46052</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -1120,8 +1049,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
         <v>46052</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -1140,8 +1069,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
         <v>46052</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -1160,8 +1089,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
         <v>46052</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -1180,8 +1109,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
         <v>46052</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -1200,8 +1129,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
         <v>46052</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -1220,8 +1149,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
         <v>46052</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -1240,8 +1169,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <v>46052</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -1260,8 +1189,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <v>46052</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -1280,8 +1209,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
         <v>46052</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1300,8 +1229,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
         <v>46052</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -1320,8 +1249,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
         <v>46052</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -1340,8 +1269,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
         <v>46052</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -1360,8 +1289,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
         <v>46055</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -1380,8 +1309,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
         <v>46055</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -1400,8 +1329,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
         <v>46055</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -1420,8 +1349,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
         <v>46056</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -1440,8 +1369,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
         <v>46056</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -1460,8 +1389,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
         <v>46056</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -1480,8 +1409,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
         <v>46057</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -1500,8 +1429,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
         <v>46057</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -1520,8 +1449,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
         <v>46057</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -1540,8 +1469,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
         <v>46057</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -1560,8 +1489,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
         <v>46057</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -1580,8 +1509,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
         <v>46057</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -1600,8 +1529,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
         <v>46057</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -1620,8 +1549,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
         <v>46058</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -1640,8 +1569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
         <v>46058</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -1660,8 +1589,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
         <v>46058</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -1680,8 +1609,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
         <v>46058</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -1700,8 +1629,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
         <v>46058</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -1720,8 +1649,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
         <v>46058</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -1740,8 +1669,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
         <v>46058</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -1760,8 +1689,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
         <v>46058</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -1780,8 +1709,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
         <v>46058</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -1800,8 +1729,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
         <v>46058</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -1820,8 +1749,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
         <v>46058</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -1840,8 +1769,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
         <v>46058</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -1860,8 +1789,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
         <v>46058</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -1880,8 +1809,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
         <v>46058</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -1900,8 +1829,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
         <v>46058</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -1920,8 +1849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
         <v>46058</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -1940,8 +1869,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="1">
         <v>46059</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -1960,8 +1889,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="1">
         <v>46059</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -1980,8 +1909,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="1">
         <v>46059</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -2000,8 +1929,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="1">
         <v>46059</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -2020,8 +1949,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="1">
         <v>46059</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -2040,8 +1969,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="1">
         <v>46059</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -2060,8 +1989,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="1">
         <v>46059</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -2080,8 +2009,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="1">
         <v>46059</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -2100,8 +2029,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
         <v>46059</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -2120,8 +2049,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
         <v>46059</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -2140,8 +2069,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
         <v>46059</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -2160,8 +2089,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
         <v>46059</v>
       </c>
       <c r="B82" s="8" t="s">
@@ -2180,8 +2109,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
         <v>46059</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -2200,8 +2129,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
         <v>46059</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -2220,8 +2149,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
         <v>46059</v>
       </c>
       <c r="B85" s="8" t="s">
@@ -2240,8 +2169,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
         <v>46059</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -2260,8 +2189,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
         <v>46059</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -2280,8 +2209,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
         <v>46059</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -2300,8 +2229,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="1">
         <v>46059</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -2320,8 +2249,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="1">
         <v>46059</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -2340,8 +2269,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="n">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="1">
         <v>46059</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -2360,8 +2289,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="n">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
         <v>46059</v>
       </c>
       <c r="B92" s="8" t="s">
@@ -2380,8 +2309,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="n">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="1">
         <v>46059</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -2400,8 +2329,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="n">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="1">
         <v>46059</v>
       </c>
       <c r="B94" s="8" t="s">
@@ -2420,8 +2349,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="n">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
         <v>46059</v>
       </c>
       <c r="B95" s="8" t="s">
@@ -2440,8 +2369,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="n">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="1">
         <v>46059</v>
       </c>
       <c r="B96" s="8" t="s">
@@ -2460,8 +2389,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="n">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="1">
         <v>46059</v>
       </c>
       <c r="B97" s="8" t="s">
@@ -2480,8 +2409,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="n">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="1">
         <v>46059</v>
       </c>
       <c r="B98" s="8" t="s">
@@ -2500,8 +2429,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="n">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="1">
         <v>46059</v>
       </c>
       <c r="B99" s="8" t="s">
@@ -2520,8 +2449,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="n">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="1">
         <v>46059</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -2540,8 +2469,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="n">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="1">
         <v>46059</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -2560,8 +2489,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="n">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="1">
         <v>46059</v>
       </c>
       <c r="B102" s="8" t="s">
@@ -2580,8 +2509,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="n">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="1">
         <v>46059</v>
       </c>
       <c r="B103" s="8" t="s">
@@ -2600,8 +2529,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="n">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="1">
         <v>46059</v>
       </c>
       <c r="B104" s="8" t="s">
@@ -2620,8 +2549,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="n">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="1">
         <v>46059</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -2640,8 +2569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="n">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="1">
         <v>46059</v>
       </c>
       <c r="B106" s="8" t="s">
@@ -2660,8 +2589,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="n">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="1">
         <v>46059</v>
       </c>
       <c r="B107" s="8" t="s">
@@ -2680,8 +2609,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="n">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="1">
         <v>46059</v>
       </c>
       <c r="B108" s="8" t="s">
@@ -2700,8 +2629,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="n">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="1">
         <v>46059</v>
       </c>
       <c r="B109" s="8" t="s">
@@ -2720,8 +2649,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="n">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="1">
         <v>46059</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -2740,8 +2669,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="n">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="1">
         <v>46059</v>
       </c>
       <c r="B111" s="8" t="s">
@@ -2760,8 +2689,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="n">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="1">
         <v>46059</v>
       </c>
       <c r="B112" s="8" t="s">
@@ -2780,8 +2709,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="n">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="1">
         <v>46059</v>
       </c>
       <c r="B113" s="8" t="s">
@@ -2800,8 +2729,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="n">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="1">
         <v>46059</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -2820,8 +2749,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="10" t="n">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="10">
         <v>46062</v>
       </c>
       <c r="B115" s="11" t="s">
@@ -2840,8 +2769,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="10" t="n">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116" s="10">
         <v>46062</v>
       </c>
       <c r="B116" s="11" t="s">
@@ -2860,8 +2789,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="10" t="n">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="10">
         <v>46063</v>
       </c>
       <c r="B117" s="11" t="s">
@@ -2880,8 +2809,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="10" t="n">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="10">
         <v>46063</v>
       </c>
       <c r="B118" s="11" t="s">
@@ -2900,8 +2829,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="10" t="n">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="10">
         <v>46063</v>
       </c>
       <c r="B119" s="11" t="s">
@@ -2920,8 +2849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="10" t="n">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="10">
         <v>46063</v>
       </c>
       <c r="B120" s="11" t="s">
@@ -2940,8 +2869,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="10" t="n">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="10">
         <v>46064</v>
       </c>
       <c r="B121" s="11" t="s">
@@ -2960,8 +2889,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="10" t="n">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="10">
         <v>46064</v>
       </c>
       <c r="B122" s="11" t="s">
@@ -2980,8 +2909,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="10" t="n">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="10">
         <v>46064</v>
       </c>
       <c r="B123" s="11" t="s">
@@ -3000,8 +2929,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="10" t="n">
+    <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10">
         <v>46064</v>
       </c>
       <c r="B124" s="11" t="s">
@@ -3020,8 +2949,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="10" t="n">
+    <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10">
         <v>46064</v>
       </c>
       <c r="B125" s="11" t="s">
@@ -3040,8 +2969,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="10" t="n">
+    <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="10">
         <v>46064</v>
       </c>
       <c r="B126" s="11" t="s">
@@ -3060,8 +2989,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="10" t="n">
+    <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="10">
         <v>46064</v>
       </c>
       <c r="B127" s="11" t="s">
@@ -3080,8 +3009,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="10" t="n">
+    <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="10">
         <v>46065</v>
       </c>
       <c r="B128" s="11" t="s">
@@ -3100,8 +3029,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="10" t="n">
+    <row r="129" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="10">
         <v>46065</v>
       </c>
       <c r="B129" s="11" t="s">
@@ -3120,8 +3049,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="10" t="n">
+    <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="10">
         <v>46065</v>
       </c>
       <c r="B130" s="11" t="s">
@@ -3140,8 +3069,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="10" t="n">
+    <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="10">
         <v>46065</v>
       </c>
       <c r="B131" s="11" t="s">
@@ -3160,8 +3089,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="10" t="n">
+    <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="10">
         <v>46066</v>
       </c>
       <c r="B132" s="11" t="s">
@@ -3180,8 +3109,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="10" t="n">
+    <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="10">
         <v>46066</v>
       </c>
       <c r="B133" s="11" t="s">
@@ -3200,8 +3129,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="10" t="n">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="10">
         <v>46069</v>
       </c>
       <c r="B134" s="11" t="s">
@@ -3220,8 +3149,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="10" t="n">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="10">
         <v>46069</v>
       </c>
       <c r="B135" s="11" t="s">
@@ -3240,8 +3169,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="10" t="n">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="10">
         <v>46071</v>
       </c>
       <c r="B136" s="11" t="s">
@@ -3260,8 +3189,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="10" t="n">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="10">
         <v>46071</v>
       </c>
       <c r="B137" s="11" t="s">
@@ -3280,8 +3209,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="10" t="n">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="10">
         <v>46071</v>
       </c>
       <c r="B138" s="11" t="s">
@@ -3300,8 +3229,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="10" t="n">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="10">
         <v>46071</v>
       </c>
       <c r="B139" s="11" t="s">
@@ -3320,8 +3249,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="10" t="n">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="10">
         <v>46071</v>
       </c>
       <c r="B140" s="11" t="s">
@@ -3340,8 +3269,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="10" t="n">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="10">
         <v>46072</v>
       </c>
       <c r="B141" s="11" t="s">
@@ -3360,8 +3289,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="10" t="n">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="10">
         <v>46072</v>
       </c>
       <c r="B142" s="11" t="s">
@@ -3380,8 +3309,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="10" t="n">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="10">
         <v>46072</v>
       </c>
       <c r="B143" s="11" t="s">
@@ -3400,8 +3329,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="10" t="n">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="10">
         <v>46072</v>
       </c>
       <c r="B144" s="11" t="s">
@@ -3420,8 +3349,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="10" t="n">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="10">
         <v>46072</v>
       </c>
       <c r="B145" s="11" t="s">
@@ -3440,8 +3369,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="10" t="n">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="10">
         <v>46072</v>
       </c>
       <c r="B146" s="11" t="s">
@@ -3460,8 +3389,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="10" t="n">
+    <row r="147" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="10">
         <v>46072</v>
       </c>
       <c r="B147" s="11" t="s">
@@ -3480,8 +3409,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="10" t="n">
+    <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="10">
         <v>46072</v>
       </c>
       <c r="B148" s="11" t="s">
@@ -3500,8 +3429,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="10" t="n">
+    <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="10">
         <v>46072</v>
       </c>
       <c r="B149" s="11" t="s">
@@ -3520,8 +3449,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="10" t="n">
+    <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="10">
         <v>46073</v>
       </c>
       <c r="B150" s="11" t="s">
@@ -3540,8 +3469,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="10" t="n">
+    <row r="151" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="10">
         <v>46073</v>
       </c>
       <c r="B151" s="11" t="s">
@@ -3560,8 +3489,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="10" t="n">
+    <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="10">
         <v>46073</v>
       </c>
       <c r="B152" s="11" t="s">
@@ -3580,8 +3509,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="10" t="n">
+    <row r="153" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="10">
         <v>46073</v>
       </c>
       <c r="B153" s="11" t="s">
@@ -3600,8 +3529,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="10" t="n">
+    <row r="154" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="10">
         <v>46073</v>
       </c>
       <c r="B154" s="11" t="s">
@@ -3620,8 +3549,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="10" t="n">
+    <row r="155" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="10">
         <v>46073</v>
       </c>
       <c r="B155" s="11" t="s">
@@ -3640,8 +3569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="10" t="n">
+    <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="10">
         <v>46073</v>
       </c>
       <c r="B156" s="11" t="s">
@@ -3660,8 +3589,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="10" t="n">
+    <row r="157" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="10">
         <v>46073</v>
       </c>
       <c r="B157" s="11" t="s">
@@ -3680,8 +3609,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="10" t="n">
+    <row r="158" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="10">
         <v>46073</v>
       </c>
       <c r="B158" s="11" t="s">
@@ -3700,8 +3629,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="10" t="n">
+    <row r="159" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="10">
         <v>46073</v>
       </c>
       <c r="B159" s="11" t="s">
@@ -3720,8 +3649,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="10" t="n">
+    <row r="160" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="10">
         <v>46073</v>
       </c>
       <c r="B160" s="11" t="s">
@@ -3740,8 +3669,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="10" t="n">
+    <row r="161" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="10">
         <v>46073</v>
       </c>
       <c r="B161" s="11" t="s">
@@ -3760,8 +3689,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="10" t="n">
+    <row r="162" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="10">
         <v>46073</v>
       </c>
       <c r="B162" s="11" t="s">
@@ -3780,8 +3709,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="10" t="n">
+    <row r="163" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="10">
         <v>46077</v>
       </c>
       <c r="B163" s="11" t="s">
@@ -3800,8 +3729,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="10" t="n">
+    <row r="164" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="10">
         <v>46077</v>
       </c>
       <c r="B164" s="11" t="s">
@@ -3820,8 +3749,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="10" t="n">
+    <row r="165" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="10">
         <v>46077</v>
       </c>
       <c r="B165" s="11" t="s">
@@ -3840,8 +3769,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="10" t="n">
+    <row r="166" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="10">
         <v>46077</v>
       </c>
       <c r="B166" s="11" t="s">
@@ -3860,8 +3789,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="10" t="n">
+    <row r="167" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="10">
         <v>46078</v>
       </c>
       <c r="B167" s="11" t="s">
@@ -3880,8 +3809,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="10" t="n">
+    <row r="168" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="10">
         <v>46078</v>
       </c>
       <c r="B168" s="11" t="s">
@@ -3900,8 +3829,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="10" t="n">
+    <row r="169" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="10">
         <v>46078</v>
       </c>
       <c r="B169" s="11" t="s">
@@ -3920,8 +3849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="10" t="n">
+    <row r="170" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="10">
         <v>46078</v>
       </c>
       <c r="B170" s="11" t="s">
@@ -3940,8 +3869,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="10" t="n">
+    <row r="171" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="10">
         <v>46079</v>
       </c>
       <c r="B171" s="11" t="s">
@@ -3960,8 +3889,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="10" t="n">
+    <row r="172" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="10">
         <v>46079</v>
       </c>
       <c r="B172" s="11" t="s">
@@ -3980,8 +3909,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="10" t="n">
+    <row r="173" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="10">
         <v>46079</v>
       </c>
       <c r="B173" s="11" t="s">
@@ -4000,8 +3929,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="10" t="n">
+    <row r="174" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="10">
         <v>46079</v>
       </c>
       <c r="B174" s="11" t="s">
@@ -4020,8 +3949,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="10" t="n">
+    <row r="175" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="10">
         <v>46080</v>
       </c>
       <c r="B175" s="11" t="s">
@@ -4040,8 +3969,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="10" t="n">
+    <row r="176" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="10">
         <v>46080</v>
       </c>
       <c r="B176" s="11" t="s">
@@ -4060,8 +3989,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="10" t="n">
+    <row r="177" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="10">
         <v>46080</v>
       </c>
       <c r="B177" s="11" t="s">
@@ -4080,8 +4009,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="10" t="n">
+    <row r="178" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="10">
         <v>46080</v>
       </c>
       <c r="B178" s="11" t="s">
@@ -4100,8 +4029,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="10" t="n">
+    <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="10">
         <v>46083</v>
       </c>
       <c r="B179" s="11" t="s">
@@ -4120,8 +4049,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="10" t="n">
+    <row r="180" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="10">
         <v>46083</v>
       </c>
       <c r="B180" s="11" t="s">
@@ -4140,8 +4069,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="n">
+    <row r="181" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="1">
         <v>46084</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -4160,8 +4089,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="n">
+    <row r="182" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="1">
         <v>46084</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -4180,8 +4109,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="n">
+    <row r="183" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="1">
         <v>46084</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -4200,8 +4129,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="n">
+    <row r="184" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="1">
         <v>46084</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -4220,8 +4149,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1" t="n">
+    <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="1">
         <v>46085</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -4240,8 +4169,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="n">
+    <row r="186" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="1">
         <v>46085</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -4260,8 +4189,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="n">
+    <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="1">
         <v>46106</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -4280,8 +4209,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="n">
+    <row r="188" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="1">
         <v>46106</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -4300,8 +4229,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="n">
+    <row r="189" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="1">
         <v>46106</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -4320,8 +4249,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="n">
+    <row r="190" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="1">
         <v>46107</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -4340,8 +4269,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="n">
+    <row r="191" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="1">
         <v>46107</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -4360,8 +4289,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="n">
+    <row r="192" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="1">
         <v>46108</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -4380,8 +4309,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="n">
+    <row r="193" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="1">
         <v>46108</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -4400,8 +4329,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="n">
+    <row r="194" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="1">
         <v>46108</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -4420,8 +4349,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="n">
+    <row r="195" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="1">
         <v>46108</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -4440,8 +4369,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="n">
+    <row r="196" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="1">
         <v>46108</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -4460,8 +4389,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="n">
+    <row r="197" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="1">
         <v>46108</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -4480,8 +4409,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="n">
+    <row r="198" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="1">
         <v>46108</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -4500,8 +4429,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="n">
+    <row r="199" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="1">
         <v>46111</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -4520,8 +4449,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1" t="n">
+    <row r="200" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="1">
         <v>46111</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -4540,8 +4469,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="n">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A201" s="1">
         <v>46111</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -4560,8 +4489,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="n">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" s="1">
         <v>46111</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -4580,8 +4509,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="n">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A203" s="1">
         <v>46112</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -4600,8 +4529,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="n">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" s="1">
         <v>46112</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -4620,8 +4549,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="n">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" s="1">
         <v>46113</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -4640,8 +4569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1" t="n">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A206" s="1">
         <v>46113</v>
       </c>
       <c r="B206" s="2" t="s">
@@ -4660,8 +4589,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="n">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A207" s="1">
         <v>46113</v>
       </c>
       <c r="B207" s="2" t="s">
@@ -4680,8 +4609,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="n">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A208" s="1">
         <v>46113</v>
       </c>
       <c r="B208" s="2" t="s">
@@ -4700,8 +4629,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1" t="n">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A209" s="1">
         <v>46114</v>
       </c>
       <c r="B209" s="2" t="s">
@@ -4720,8 +4649,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="1" t="n">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A210" s="1">
         <v>46114</v>
       </c>
       <c r="B210" s="2" t="s">
@@ -4740,8 +4669,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="1" t="n">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A211" s="1">
         <v>46114</v>
       </c>
       <c r="B211" s="2" t="s">
@@ -4760,8 +4689,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="1" t="n">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A212" s="1">
         <v>46114</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -4780,8 +4709,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="n">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" s="1">
         <v>46114</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -4800,8 +4729,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="1" t="n">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" s="1">
         <v>46114</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -4820,8 +4749,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="n">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
         <v>46115</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -4840,8 +4769,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="1" t="n">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
         <v>46115</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -4860,8 +4789,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1" t="n">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
         <v>46115</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -4880,8 +4809,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="1" t="n">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
         <v>46115</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -4900,8 +4829,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="1" t="n">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A219" s="1">
         <v>46183</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -4920,8 +4849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="1" t="n">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A220" s="1">
         <v>46183</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -4940,8 +4869,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1" t="n">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A221" s="1">
         <v>46183</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -4960,8 +4889,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="1" t="n">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A222" s="1">
         <v>46183</v>
       </c>
       <c r="B222" s="2" t="s">
@@ -4980,8 +4909,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="1" t="n">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A223" s="1">
         <v>46183</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -5000,8 +4929,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="1" t="n">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A224" s="1">
         <v>46183</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -5020,8 +4949,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="1" t="n">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A225" s="1">
         <v>46184</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -5040,8 +4969,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="1" t="n">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A226" s="1">
         <v>46184</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -5060,8 +4989,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="1" t="n">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A227" s="1">
         <v>46184</v>
       </c>
       <c r="B227" s="2" t="s">
@@ -5080,8 +5009,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="n">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A228" s="1">
         <v>46184</v>
       </c>
       <c r="B228" s="2" t="s">
@@ -5100,8 +5029,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="1" t="n">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A229" s="1">
         <v>46185</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -5120,8 +5049,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="n">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" s="1">
         <v>46185</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -5140,8 +5069,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="n">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A231" s="1">
         <v>46185</v>
       </c>
       <c r="B231" s="2" t="s">
@@ -5160,8 +5089,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="1" t="n">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A232" s="1">
         <v>46185</v>
       </c>
       <c r="B232" s="2" t="s">
@@ -5180,8 +5109,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="n">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A233" s="1">
         <v>46185</v>
       </c>
       <c r="B233" s="2" t="s">
@@ -5200,8 +5129,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="1" t="n">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A234" s="1">
         <v>46185</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -5220,8 +5149,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="1" t="n">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A235" s="1">
         <v>46185</v>
       </c>
       <c r="B235" s="2" t="s">
@@ -5240,8 +5169,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="1" t="n">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A236" s="1">
         <v>46185</v>
       </c>
       <c r="B236" s="2" t="s">
@@ -5260,8 +5189,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="n">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A237" s="1">
         <v>46185</v>
       </c>
       <c r="B237" s="2" t="s">
@@ -5280,8 +5209,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="1" t="n">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" s="1">
         <v>46185</v>
       </c>
       <c r="B238" s="2" t="s">
@@ -5300,8 +5229,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="1" t="n">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A239" s="1">
         <v>46185</v>
       </c>
       <c r="B239" s="2" t="s">
@@ -5320,8 +5249,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="1" t="n">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" s="1">
         <v>46185</v>
       </c>
       <c r="B240" s="2" t="s">
@@ -5340,8 +5269,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="1" t="n">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" s="1">
         <v>46185</v>
       </c>
       <c r="B241" s="2" t="s">
@@ -5360,8 +5289,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1" t="n">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A242" s="1">
         <v>46185</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -5380,8 +5309,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="1" t="n">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A243" s="1">
         <v>46185</v>
       </c>
       <c r="B243" s="2" t="s">
@@ -5400,8 +5329,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="1" t="n">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A244" s="1">
         <v>46185</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -5420,8 +5349,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1" t="n">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A245" s="1">
         <v>46185</v>
       </c>
       <c r="B245" s="2" t="s">
@@ -5440,8 +5369,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="1" t="n">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A246" s="1">
         <v>46185</v>
       </c>
       <c r="B246" s="2" t="s">
@@ -5460,8 +5389,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="1" t="n">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A247" s="1">
         <v>46185</v>
       </c>
       <c r="B247" s="2" t="s">
@@ -5480,8 +5409,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="1" t="n">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A248" s="1">
         <v>46185</v>
       </c>
       <c r="B248" s="2" t="s">
@@ -5500,8 +5429,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="1" t="n">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A249" s="1">
         <v>46185</v>
       </c>
       <c r="B249" s="2" t="s">
@@ -5520,8 +5449,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="1" t="n">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A250" s="1">
         <v>46185</v>
       </c>
       <c r="B250" s="2" t="s">
@@ -5540,8 +5469,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="1" t="n">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A251" s="1">
         <v>46185</v>
       </c>
       <c r="B251" s="2" t="s">
@@ -5560,8 +5489,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="1" t="n">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A252" s="1">
         <v>46185</v>
       </c>
       <c r="B252" s="2" t="s">
@@ -5580,8 +5509,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="1" t="n">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A253" s="1">
         <v>46185</v>
       </c>
       <c r="B253" s="2" t="s">
@@ -5600,8 +5529,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="1" t="n">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A254" s="1">
         <v>46188</v>
       </c>
       <c r="B254" s="2" t="s">
@@ -5620,8 +5549,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="1" t="n">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A255" s="1">
         <v>46188</v>
       </c>
       <c r="B255" s="2" t="s">
@@ -5640,8 +5569,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="1" t="n">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A256" s="1">
         <v>46188</v>
       </c>
       <c r="B256" s="2" t="s">
@@ -5660,8 +5589,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="1" t="n">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A257" s="1">
         <v>46188</v>
       </c>
       <c r="B257" s="2" t="s">
@@ -5680,8 +5609,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="1" t="n">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A258" s="1">
         <v>46189</v>
       </c>
       <c r="B258" s="2" t="s">
@@ -5700,8 +5629,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="1" t="n">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A259" s="1">
         <v>46189</v>
       </c>
       <c r="B259" s="2" t="s">
@@ -5720,8 +5649,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="1" t="n">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A260" s="1">
         <v>46189</v>
       </c>
       <c r="B260" s="2" t="s">
@@ -5740,8 +5669,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="1" t="n">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A261" s="1">
         <v>46190</v>
       </c>
       <c r="B261" s="2" t="s">
@@ -5760,8 +5689,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1" t="n">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A262" s="1">
         <v>46190</v>
       </c>
       <c r="B262" s="2" t="s">
@@ -5780,8 +5709,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="1" t="n">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A263" s="1">
         <v>46190</v>
       </c>
       <c r="B263" s="2" t="s">
@@ -5800,8 +5729,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="1" t="n">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A264" s="1">
         <v>46190</v>
       </c>
       <c r="B264" s="2" t="s">
@@ -5820,8 +5749,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="1" t="n">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A265" s="1">
         <v>46190</v>
       </c>
       <c r="B265" s="2" t="s">
@@ -5840,8 +5769,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="1" t="n">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A266" s="1">
         <v>46190</v>
       </c>
       <c r="B266" s="2" t="s">
@@ -5860,8 +5789,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="1" t="n">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A267" s="1">
         <v>46190</v>
       </c>
       <c r="B267" s="2" t="s">
@@ -5880,8 +5809,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="1" t="n">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A268" s="1">
         <v>46190</v>
       </c>
       <c r="B268" s="2" t="s">
@@ -5900,8 +5829,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="1" t="n">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A269" s="1">
         <v>46190</v>
       </c>
       <c r="B269" s="2" t="s">
@@ -5920,8 +5849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="1" t="n">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A270" s="1">
         <v>46190</v>
       </c>
       <c r="B270" s="2" t="s">
@@ -5940,8 +5869,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="1" t="n">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A271" s="1">
         <v>46190</v>
       </c>
       <c r="B271" s="2" t="s">
@@ -5960,8 +5889,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="1" t="n">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A272" s="1">
         <v>46191</v>
       </c>
       <c r="B272" s="2" t="s">
@@ -5980,8 +5909,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="1" t="n">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A273" s="1">
         <v>46191</v>
       </c>
       <c r="B273" s="2" t="s">
@@ -6000,8 +5929,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="1" t="n">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" s="1">
         <v>46191</v>
       </c>
       <c r="B274" s="2" t="s">
@@ -6020,8 +5949,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="1" t="n">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" s="1">
         <v>46191</v>
       </c>
       <c r="B275" s="2" t="s">
@@ -6040,8 +5969,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="1" t="n">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" s="1">
         <v>46191</v>
       </c>
       <c r="B276" s="2" t="s">
@@ -6060,8 +5989,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="1" t="n">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A277" s="1">
         <v>46191</v>
       </c>
       <c r="B277" s="2" t="s">
@@ -6080,8 +6009,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="1" t="n">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A278" s="1">
         <v>46191</v>
       </c>
       <c r="B278" s="2" t="s">
@@ -6100,8 +6029,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="1" t="n">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A279" s="1">
         <v>46191</v>
       </c>
       <c r="B279" s="2" t="s">
@@ -6120,8 +6049,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="1" t="n">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A280" s="1">
         <v>46191</v>
       </c>
       <c r="B280" s="2" t="s">
@@ -6140,8 +6069,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="1" t="n">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A281" s="1">
         <v>46191</v>
       </c>
       <c r="B281" s="2" t="s">
@@ -6160,8 +6089,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="1" t="n">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" s="1">
         <v>46195</v>
       </c>
       <c r="B282" s="2" t="s">
@@ -6180,8 +6109,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="1" t="n">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" s="1">
         <v>46195</v>
       </c>
       <c r="B283" s="2" t="s">
@@ -6200,8 +6129,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="1" t="n">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" s="1">
         <v>46195</v>
       </c>
       <c r="B284" s="2" t="s">
@@ -6220,8 +6149,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="1" t="n">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A285" s="1">
         <v>46196</v>
       </c>
       <c r="B285" s="2" t="s">
@@ -6240,8 +6169,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="1" t="n">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A286" s="1">
         <v>46196</v>
       </c>
       <c r="B286" s="2" t="s">
@@ -6260,8 +6189,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="1" t="n">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" s="1">
         <v>46196</v>
       </c>
       <c r="B287" s="2" t="s">
@@ -6280,8 +6209,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="1" t="n">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" s="1">
         <v>46196</v>
       </c>
       <c r="B288" s="2" t="s">
@@ -6300,8 +6229,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="1" t="n">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="1">
         <v>46197</v>
       </c>
       <c r="B289" s="2" t="s">
@@ -6320,8 +6249,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="1" t="n">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A290" s="1">
         <v>46197</v>
       </c>
       <c r="B290" s="2" t="s">
@@ -6340,8 +6269,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="1" t="n">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A291" s="1">
         <v>46197</v>
       </c>
       <c r="B291" s="2" t="s">
@@ -6360,8 +6289,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="1" t="n">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" s="1">
         <v>46197</v>
       </c>
       <c r="B292" s="2" t="s">
@@ -6380,8 +6309,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="1" t="n">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A293" s="1">
         <v>46197</v>
       </c>
       <c r="B293" s="2" t="s">
@@ -6400,8 +6329,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="1" t="n">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" s="1">
         <v>46197</v>
       </c>
       <c r="B294" s="2" t="s">
@@ -6420,8 +6349,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="1" t="n">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" s="1">
         <v>46197</v>
       </c>
       <c r="B295" s="2" t="s">
@@ -6440,8 +6369,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="1" t="n">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="1">
         <v>46197</v>
       </c>
       <c r="B296" s="2" t="s">
@@ -6460,8 +6389,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="1" t="n">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="1">
         <v>46197</v>
       </c>
       <c r="B297" s="2" t="s">
@@ -6480,8 +6409,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="1" t="n">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A298" s="1">
         <v>46199</v>
       </c>
       <c r="B298" s="2" t="s">
@@ -6500,8 +6429,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="1" t="n">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A299" s="1">
         <v>46199</v>
       </c>
       <c r="B299" s="2" t="s">
@@ -6520,8 +6449,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="1" t="n">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" s="1">
         <v>46199</v>
       </c>
       <c r="B300" s="2" t="s">
@@ -6540,8 +6469,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="1" t="n">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" s="1">
         <v>46199</v>
       </c>
       <c r="B301" s="2" t="s">
@@ -6560,8 +6489,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="1" t="n">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A302" s="1">
         <v>46199</v>
       </c>
       <c r="B302" s="2" t="s">
@@ -6580,13 +6509,728 @@
         <v>45</v>
       </c>
     </row>
+    <row r="303" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A303" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A304" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A305" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A306" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A307" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A308" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A309" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A310" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A311" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A312" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A313" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A314" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A315" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A316" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A317" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A318" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A319" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A320" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A321" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A322" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A323" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F323" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A324" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A325" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F325" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A326" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F326" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A327" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A328" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F328" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A329" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A330" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F330" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F331" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A332" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A333" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F333" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A334" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F334" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A335" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F335" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A336" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F336" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A337" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F337" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A338" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CD0106-B3A3-4D64-B2CB-F146DBF8AA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DC7DA2-47DE-45A8-B804-51DF2B440847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="47">
   <si>
     <t>date</t>
   </si>
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G338"/>
+  <dimension ref="A1:G370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
@@ -7229,6 +7229,646 @@
         <v>10</v>
       </c>
     </row>
+    <row r="339" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A339" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A340" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A341" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F341" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A342" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F342" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A343" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F343" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A344" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F344" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A345" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F345" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A346" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A347" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F347" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A348" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F348" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A349" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F349" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A350" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F350" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A351" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F351" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A352" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F352" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A353" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F353" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A354" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F354" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A355" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F355" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A356" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A357" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A358" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A359" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A360" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A361" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F361" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A362" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A363" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F363" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A364" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A365" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A366" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A367" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A368" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A369" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F369" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A370" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F370" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DC7DA2-47DE-45A8-B804-51DF2B440847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C94E258-D23B-4264-BC1A-FD7E2CC9E803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="345" yWindow="1080" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matchs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="48">
   <si>
     <t>date</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>Aude</t>
+  </si>
+  <si>
+    <t>Morgane</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
@@ -7869,6 +7872,326 @@
         <v>10</v>
       </c>
     </row>
+    <row r="371" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A371" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F371" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A372" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F372" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A373" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F373" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A374" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F374" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A375" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F375" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A376" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F376" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A377" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F377" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A378" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F378" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A379" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F379" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A380" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F380" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A381" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F381" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A382" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F382" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A383" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F383" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A384" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F384" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A385" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F385" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A386" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F386" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesarili\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alliorem/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C94E258-D23B-4264-BC1A-FD7E2CC9E803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7523030-82D8-864D-918D-B1A607E9D06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="345" yWindow="1080" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-24660" yWindow="4120" windowWidth="21600" windowHeight="12640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matchs" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="48">
   <si>
     <t>date</t>
   </si>
@@ -254,19 +254,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,19 +459,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G386"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G401"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -492,7 +491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46048</v>
       </c>
@@ -512,7 +511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46048</v>
       </c>
@@ -532,7 +531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46049</v>
       </c>
@@ -552,7 +551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46049</v>
       </c>
@@ -572,7 +571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46049</v>
       </c>
@@ -592,7 +591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46049</v>
       </c>
@@ -612,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46049</v>
       </c>
@@ -632,7 +631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46049</v>
       </c>
@@ -652,7 +651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46049</v>
       </c>
@@ -672,7 +671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46049</v>
       </c>
@@ -692,7 +691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46049</v>
       </c>
@@ -712,7 +711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46049</v>
       </c>
@@ -732,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46050</v>
       </c>
@@ -752,7 +751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46050</v>
       </c>
@@ -772,7 +771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46050</v>
       </c>
@@ -792,7 +791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46050</v>
       </c>
@@ -812,7 +811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46050</v>
       </c>
@@ -832,7 +831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46051</v>
       </c>
@@ -852,7 +851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46052</v>
       </c>
@@ -872,7 +871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46052</v>
       </c>
@@ -892,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46052</v>
       </c>
@@ -912,7 +911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46052</v>
       </c>
@@ -932,7 +931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46052</v>
       </c>
@@ -952,7 +951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46052</v>
       </c>
@@ -972,7 +971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46052</v>
       </c>
@@ -992,7 +991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46052</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46052</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46052</v>
       </c>
@@ -1052,7 +1051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46052</v>
       </c>
@@ -1092,7 +1091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46052</v>
       </c>
@@ -1112,7 +1111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46052</v>
       </c>
@@ -1132,7 +1131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46052</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46052</v>
       </c>
@@ -1172,7 +1171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46052</v>
       </c>
@@ -1192,7 +1191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46052</v>
       </c>
@@ -1212,7 +1211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46052</v>
       </c>
@@ -1232,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46052</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46052</v>
       </c>
@@ -1272,7 +1271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46052</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46055</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46055</v>
       </c>
@@ -1332,7 +1331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46055</v>
       </c>
@@ -1352,7 +1351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46056</v>
       </c>
@@ -1372,7 +1371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46056</v>
       </c>
@@ -1392,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46056</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46057</v>
       </c>
@@ -1432,7 +1431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46057</v>
       </c>
@@ -1452,7 +1451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46057</v>
       </c>
@@ -1472,7 +1471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46057</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46057</v>
       </c>
@@ -1512,7 +1511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46057</v>
       </c>
@@ -1532,7 +1531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46057</v>
       </c>
@@ -1552,7 +1551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46058</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46058</v>
       </c>
@@ -1592,7 +1591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46058</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46058</v>
       </c>
@@ -1632,7 +1631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46058</v>
       </c>
@@ -1652,7 +1651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46058</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46058</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46058</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46058</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46058</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46058</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46058</v>
       </c>
@@ -1792,7 +1791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46058</v>
       </c>
@@ -1812,7 +1811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46058</v>
       </c>
@@ -1832,7 +1831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46058</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46058</v>
       </c>
@@ -1872,7 +1871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46059</v>
       </c>
@@ -1892,7 +1891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46059</v>
       </c>
@@ -1912,7 +1911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46059</v>
       </c>
@@ -1932,7 +1931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46059</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46059</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46059</v>
       </c>
@@ -1992,7 +1991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46059</v>
       </c>
@@ -2012,7 +2011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46059</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46059</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46059</v>
       </c>
@@ -2072,7 +2071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46059</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46059</v>
       </c>
@@ -2112,7 +2111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46059</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46059</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46059</v>
       </c>
@@ -2172,7 +2171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46059</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46059</v>
       </c>
@@ -2212,7 +2211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46059</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46059</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46059</v>
       </c>
@@ -2272,7 +2271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46059</v>
       </c>
@@ -2292,7 +2291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46059</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46059</v>
       </c>
@@ -2332,7 +2331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46059</v>
       </c>
@@ -2352,7 +2351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46059</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46059</v>
       </c>
@@ -2392,7 +2391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46059</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46059</v>
       </c>
@@ -2432,7 +2431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46059</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46059</v>
       </c>
@@ -2472,7 +2471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46059</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46059</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46059</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46059</v>
       </c>
@@ -2552,7 +2551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46059</v>
       </c>
@@ -2572,7 +2571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46059</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46059</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46059</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46059</v>
       </c>
@@ -2652,7 +2651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46059</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46059</v>
       </c>
@@ -2692,7 +2691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46059</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46059</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46059</v>
       </c>
@@ -2752,1327 +2751,1327 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>46062</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C115" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E115" s="11" t="s">
+      <c r="C115" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F115" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F115" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>46062</v>
       </c>
-      <c r="B116" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" s="11" t="s">
+      <c r="B116" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D116" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>46063</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D117" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E117" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F117" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E117" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>46063</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E118" s="11" t="s">
+      <c r="D118" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F118" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F118" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>46063</v>
       </c>
-      <c r="B119" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="11" t="s">
+      <c r="B119" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F119" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F119" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>46063</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D120" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E120" s="11" t="s">
+      <c r="D120" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F120" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F120" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>46064</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" s="11" t="s">
+      <c r="C121" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F121" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F121" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>46064</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D122" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E122" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E122" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>46064</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E123" s="11" t="s">
+      <c r="C123" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F123" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F123" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>46064</v>
       </c>
-      <c r="B124" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" s="11" t="s">
+      <c r="B124" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F124" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F124" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>46064</v>
       </c>
-      <c r="B125" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>46064</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C126" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F126" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>46064</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C127" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C127" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>46065</v>
       </c>
-      <c r="B128" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" s="11" t="s">
+      <c r="B128" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E128" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>46065</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C129" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D129" s="11" t="s">
+      <c r="C129" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F129" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F129" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>46065</v>
       </c>
-      <c r="B130" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130" s="11" t="s">
+      <c r="B130" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F130" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F130" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>46065</v>
       </c>
-      <c r="B131" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="11" t="s">
+      <c r="B131" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E131" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F131" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F131" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>46066</v>
       </c>
-      <c r="B132" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D132" s="11" t="s">
+      <c r="B132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D132" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F132" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F132" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>46066</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D133" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="11" t="s">
+      <c r="D133" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F133" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F133" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>46069</v>
       </c>
-      <c r="B134" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" s="11" t="s">
+      <c r="B134" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D134" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E134" s="11" t="s">
+      <c r="D134" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F134" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F134" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>46069</v>
       </c>
-      <c r="B135" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135" s="11" t="s">
+      <c r="B135" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E135" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F135" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F135" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>46071</v>
       </c>
-      <c r="B136" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C136" s="11" t="s">
+      <c r="B136" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D136" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F136" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>46071</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" s="11" t="s">
+      <c r="B137" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D137" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E137" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D137" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>46071</v>
       </c>
-      <c r="B138" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D138" s="11" t="s">
+      <c r="B138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F138" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F138" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>46071</v>
       </c>
-      <c r="B139" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D139" s="11" t="s">
+      <c r="B139" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D139" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>46071</v>
       </c>
-      <c r="B140" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" s="11" t="s">
+      <c r="B140" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D140" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E140" s="11" t="s">
+      <c r="D140" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F140" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F140" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>46072</v>
       </c>
-      <c r="B141" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D141" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F141" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B141" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>46072</v>
       </c>
-      <c r="B142" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D142" s="11" t="s">
+      <c r="B142" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D142" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="E142" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F142" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F142" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>46072</v>
       </c>
-      <c r="B143" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" s="11" t="s">
+      <c r="B143" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D143" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" s="11" t="s">
+      <c r="D143" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F143" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F143" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>46072</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C144" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D144" s="11" t="s">
+      <c r="C144" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E144" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F144" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E144" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>46072</v>
       </c>
-      <c r="B145" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D145" s="11" t="s">
+      <c r="B145" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E145" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F145" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E145" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>46072</v>
       </c>
-      <c r="B146" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D146" s="11" t="s">
+      <c r="B146" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F146" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E146" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>46072</v>
       </c>
-      <c r="B147" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D147" s="11" t="s">
+      <c r="B147" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E147" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>46072</v>
       </c>
-      <c r="B148" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E148" s="11" t="s">
+      <c r="B148" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F148" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>46072</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F149" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C149" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>46073</v>
       </c>
-      <c r="B150" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E150" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B150" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>46073</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D151" s="11" t="s">
+      <c r="D151" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F151" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F151" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>46073</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C152" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E152" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C152" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>46073</v>
       </c>
-      <c r="B153" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D153" s="11" t="s">
+      <c r="B153" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E153" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E153" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>46073</v>
       </c>
-      <c r="B154" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C154" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154" s="11" t="s">
+      <c r="B154" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E154" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E154" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>46073</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="C155" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D155" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E155" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F155" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>46073</v>
       </c>
-      <c r="B156" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156" s="11" t="s">
+      <c r="B156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F156" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F156" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>46073</v>
       </c>
-      <c r="B157" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>46073</v>
       </c>
-      <c r="B158" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C158" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E158" s="11" t="s">
+      <c r="B158" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F158" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F158" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>46073</v>
       </c>
-      <c r="B159" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>46073</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C160" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C160" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>46073</v>
       </c>
-      <c r="B161" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E161" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F161" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B161" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>46073</v>
       </c>
-      <c r="B162" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D162" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F162" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B162" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>46077</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C163" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D163" s="11" t="s">
+      <c r="C163" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D163" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E163" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E163" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>46077</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C164" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D164" s="11" t="s">
+      <c r="C164" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E164" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F164" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E164" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>46077</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C165" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="11" t="s">
+      <c r="C165" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D165" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E165" s="11" t="s">
+      <c r="E165" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F165" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F165" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>46077</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C166" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E166" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F166" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C166" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>46078</v>
       </c>
-      <c r="B167" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D167" s="11" t="s">
+      <c r="B167" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D167" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E167" s="11" t="s">
+      <c r="E167" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F167" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F167" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>46078</v>
       </c>
-      <c r="B168" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C168" s="11" t="s">
+      <c r="B168" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D168" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E168" s="11" t="s">
+      <c r="D168" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F168" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F168" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>46078</v>
       </c>
-      <c r="B169" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C169" s="11" t="s">
+      <c r="B169" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D169" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E169" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D169" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>46078</v>
       </c>
-      <c r="B170" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D170" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" s="11" t="s">
+      <c r="B170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F170" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F170" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>46079</v>
       </c>
-      <c r="B171" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C171" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D171" s="11" t="s">
+      <c r="B171" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E171" s="11" t="s">
+      <c r="E171" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F171" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F171" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>46079</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D172" s="11" t="s">
+      <c r="D172" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E172" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F172" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E172" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>46079</v>
       </c>
-      <c r="B173" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E173" s="11" t="s">
+      <c r="B173" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F173" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F173" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>46079</v>
       </c>
-      <c r="B174" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C174" s="11" t="s">
+      <c r="B174" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D174" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E174" s="11" t="s">
+      <c r="D174" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F174" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F174" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>46080</v>
       </c>
-      <c r="B175" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D175" s="11" t="s">
+      <c r="B175" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D175" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E175" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F175" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E175" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>46080</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="C176" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D176" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E176" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F176" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D176" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>46080</v>
       </c>
-      <c r="B177" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" s="11" t="s">
+      <c r="B177" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="D177" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E177" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E177" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>46080</v>
       </c>
-      <c r="B178" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C178" s="11" t="s">
+      <c r="B178" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D178" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E178" s="11" t="s">
+      <c r="D178" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F178" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F178" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>46083</v>
       </c>
-      <c r="B179" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C179" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D179" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E179" s="11" t="s">
+      <c r="B179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F179" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F179" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>46083</v>
       </c>
-      <c r="B180" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C180" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D180" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E180" s="11" t="s">
+      <c r="B180" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E180" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F180" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F180" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46084</v>
       </c>
@@ -4092,7 +4091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46084</v>
       </c>
@@ -4112,7 +4111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46084</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46084</v>
       </c>
@@ -4152,7 +4151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46085</v>
       </c>
@@ -4172,7 +4171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46085</v>
       </c>
@@ -4192,7 +4191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46106</v>
       </c>
@@ -4212,7 +4211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46106</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46106</v>
       </c>
@@ -4252,7 +4251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46107</v>
       </c>
@@ -4272,7 +4271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46107</v>
       </c>
@@ -4292,7 +4291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46108</v>
       </c>
@@ -4312,7 +4311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46108</v>
       </c>
@@ -4332,7 +4331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46108</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46108</v>
       </c>
@@ -4372,7 +4371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46108</v>
       </c>
@@ -4392,7 +4391,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46108</v>
       </c>
@@ -4412,7 +4411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46108</v>
       </c>
@@ -4432,7 +4431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46111</v>
       </c>
@@ -4452,7 +4451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46111</v>
       </c>
@@ -4472,7 +4471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46111</v>
       </c>
@@ -4492,7 +4491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46111</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46112</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46112</v>
       </c>
@@ -4552,7 +4551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46113</v>
       </c>
@@ -4572,7 +4571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46113</v>
       </c>
@@ -4592,7 +4591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46113</v>
       </c>
@@ -4612,7 +4611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46113</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46114</v>
       </c>
@@ -4652,7 +4651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46114</v>
       </c>
@@ -4672,7 +4671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46114</v>
       </c>
@@ -4692,7 +4691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46114</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46114</v>
       </c>
@@ -4732,7 +4731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46114</v>
       </c>
@@ -4752,7 +4751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>46115</v>
       </c>
@@ -4772,7 +4771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46115</v>
       </c>
@@ -4792,7 +4791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46115</v>
       </c>
@@ -4812,7 +4811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46115</v>
       </c>
@@ -4832,7 +4831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46183</v>
       </c>
@@ -4852,7 +4851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46183</v>
       </c>
@@ -4872,7 +4871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46183</v>
       </c>
@@ -4892,7 +4891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46183</v>
       </c>
@@ -4912,7 +4911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46183</v>
       </c>
@@ -4932,7 +4931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46183</v>
       </c>
@@ -4952,7 +4951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46184</v>
       </c>
@@ -4972,7 +4971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>46184</v>
       </c>
@@ -4992,7 +4991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>46184</v>
       </c>
@@ -5012,7 +5011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>46184</v>
       </c>
@@ -5032,7 +5031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>46185</v>
       </c>
@@ -5052,7 +5051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>46185</v>
       </c>
@@ -5072,7 +5071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>46185</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>46185</v>
       </c>
@@ -5112,7 +5111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>46185</v>
       </c>
@@ -5132,7 +5131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>46185</v>
       </c>
@@ -5152,7 +5151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>46185</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>46185</v>
       </c>
@@ -5192,7 +5191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46185</v>
       </c>
@@ -5212,7 +5211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46185</v>
       </c>
@@ -5232,7 +5231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46185</v>
       </c>
@@ -5252,7 +5251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46185</v>
       </c>
@@ -5272,7 +5271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46185</v>
       </c>
@@ -5292,7 +5291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46185</v>
       </c>
@@ -5312,7 +5311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>46185</v>
       </c>
@@ -5332,7 +5331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>46185</v>
       </c>
@@ -5352,7 +5351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46185</v>
       </c>
@@ -5372,7 +5371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46185</v>
       </c>
@@ -5392,7 +5391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46185</v>
       </c>
@@ -5412,7 +5411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46185</v>
       </c>
@@ -5432,7 +5431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46185</v>
       </c>
@@ -5452,7 +5451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46185</v>
       </c>
@@ -5472,7 +5471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46185</v>
       </c>
@@ -5492,7 +5491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46185</v>
       </c>
@@ -5512,7 +5511,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46185</v>
       </c>
@@ -5532,7 +5531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46188</v>
       </c>
@@ -5552,7 +5551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46188</v>
       </c>
@@ -5572,7 +5571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>46188</v>
       </c>
@@ -5592,7 +5591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46188</v>
       </c>
@@ -5612,7 +5611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>46189</v>
       </c>
@@ -5632,7 +5631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>46189</v>
       </c>
@@ -5652,7 +5651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>46189</v>
       </c>
@@ -5672,7 +5671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>46190</v>
       </c>
@@ -5692,7 +5691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>46190</v>
       </c>
@@ -5712,7 +5711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>46190</v>
       </c>
@@ -5732,7 +5731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>46190</v>
       </c>
@@ -5752,7 +5751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>46190</v>
       </c>
@@ -5772,7 +5771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>46190</v>
       </c>
@@ -5792,7 +5791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>46190</v>
       </c>
@@ -5812,7 +5811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>46190</v>
       </c>
@@ -5832,7 +5831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>46190</v>
       </c>
@@ -5852,7 +5851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>46190</v>
       </c>
@@ -5872,7 +5871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>46190</v>
       </c>
@@ -5892,7 +5891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>46191</v>
       </c>
@@ -5912,7 +5911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>46191</v>
       </c>
@@ -5932,7 +5931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>46191</v>
       </c>
@@ -5952,7 +5951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>46191</v>
       </c>
@@ -5972,7 +5971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>46191</v>
       </c>
@@ -5992,7 +5991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>46191</v>
       </c>
@@ -6012,7 +6011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>46191</v>
       </c>
@@ -6032,7 +6031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>46191</v>
       </c>
@@ -6052,7 +6051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>46191</v>
       </c>
@@ -6072,7 +6071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>46191</v>
       </c>
@@ -6092,7 +6091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>46195</v>
       </c>
@@ -6112,7 +6111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>46195</v>
       </c>
@@ -6132,7 +6131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>46195</v>
       </c>
@@ -6152,7 +6151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>46196</v>
       </c>
@@ -6172,7 +6171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>46196</v>
       </c>
@@ -6192,7 +6191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>46196</v>
       </c>
@@ -6212,7 +6211,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>46196</v>
       </c>
@@ -6232,7 +6231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>46197</v>
       </c>
@@ -6252,7 +6251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>46197</v>
       </c>
@@ -6272,7 +6271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>46197</v>
       </c>
@@ -6292,7 +6291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>46197</v>
       </c>
@@ -6312,7 +6311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>46197</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>46197</v>
       </c>
@@ -6352,7 +6351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>46197</v>
       </c>
@@ -6372,7 +6371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>46197</v>
       </c>
@@ -6392,7 +6391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>46197</v>
       </c>
@@ -6412,7 +6411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>46199</v>
       </c>
@@ -6432,7 +6431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>46199</v>
       </c>
@@ -6452,7 +6451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>46199</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>46199</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>46199</v>
       </c>
@@ -6512,7 +6511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>46199</v>
       </c>
@@ -6532,7 +6531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>46199</v>
       </c>
@@ -6552,7 +6551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>46199</v>
       </c>
@@ -6572,7 +6571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46202</v>
       </c>
@@ -6592,7 +6591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46202</v>
       </c>
@@ -6612,7 +6611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46202</v>
       </c>
@@ -6632,7 +6631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46203</v>
       </c>
@@ -6652,7 +6651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>46203</v>
       </c>
@@ -6672,7 +6671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>46204</v>
       </c>
@@ -6692,7 +6691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>46204</v>
       </c>
@@ -6712,7 +6711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>46204</v>
       </c>
@@ -6732,7 +6731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>46204</v>
       </c>
@@ -6752,7 +6751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>46204</v>
       </c>
@@ -6772,7 +6771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>46205</v>
       </c>
@@ -6792,7 +6791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>46205</v>
       </c>
@@ -6812,7 +6811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>46205</v>
       </c>
@@ -6832,7 +6831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>46205</v>
       </c>
@@ -6852,7 +6851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>46206</v>
       </c>
@@ -6872,7 +6871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>46206</v>
       </c>
@@ -6892,7 +6891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>46206</v>
       </c>
@@ -6912,7 +6911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>46206</v>
       </c>
@@ -6932,7 +6931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>46206</v>
       </c>
@@ -6952,7 +6951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>46206</v>
       </c>
@@ -6972,7 +6971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>46206</v>
       </c>
@@ -6992,7 +6991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>46206</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>46206</v>
       </c>
@@ -7032,7 +7031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>46206</v>
       </c>
@@ -7052,7 +7051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>46206</v>
       </c>
@@ -7072,7 +7071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>46206</v>
       </c>
@@ -7092,7 +7091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>46209</v>
       </c>
@@ -7112,7 +7111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>46209</v>
       </c>
@@ -7132,7 +7131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46209</v>
       </c>
@@ -7152,7 +7151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46210</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46210</v>
       </c>
@@ -7192,7 +7191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46210</v>
       </c>
@@ -7212,7 +7211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>46210</v>
       </c>
@@ -7232,7 +7231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>46211</v>
       </c>
@@ -7252,7 +7251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>46211</v>
       </c>
@@ -7272,7 +7271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>46211</v>
       </c>
@@ -7292,7 +7291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>46211</v>
       </c>
@@ -7312,7 +7311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>46212</v>
       </c>
@@ -7332,7 +7331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>46212</v>
       </c>
@@ -7352,7 +7351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>46212</v>
       </c>
@@ -7372,7 +7371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>46212</v>
       </c>
@@ -7392,7 +7391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>46213</v>
       </c>
@@ -7412,7 +7411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>46213</v>
       </c>
@@ -7432,7 +7431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>46213</v>
       </c>
@@ -7452,7 +7451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>46213</v>
       </c>
@@ -7472,7 +7471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>46216</v>
       </c>
@@ -7492,7 +7491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>46216</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46216</v>
       </c>
@@ -7532,7 +7531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46216</v>
       </c>
@@ -7552,7 +7551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46216</v>
       </c>
@@ -7572,7 +7571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46216</v>
       </c>
@@ -7592,7 +7591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46216</v>
       </c>
@@ -7612,7 +7611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46216</v>
       </c>
@@ -7632,7 +7631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46216</v>
       </c>
@@ -7652,7 +7651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>46218</v>
       </c>
@@ -7672,7 +7671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>46218</v>
       </c>
@@ -7692,7 +7691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46218</v>
       </c>
@@ -7712,7 +7711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46218</v>
       </c>
@@ -7732,7 +7731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46218</v>
       </c>
@@ -7752,7 +7751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46219</v>
       </c>
@@ -7772,7 +7771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>46219</v>
       </c>
@@ -7792,7 +7791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>46219</v>
       </c>
@@ -7812,7 +7811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>46219</v>
       </c>
@@ -7832,7 +7831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>46219</v>
       </c>
@@ -7852,7 +7851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>46219</v>
       </c>
@@ -7872,7 +7871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>46220</v>
       </c>
@@ -7892,7 +7891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>46220</v>
       </c>
@@ -7912,7 +7911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>46220</v>
       </c>
@@ -7932,7 +7931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>46220</v>
       </c>
@@ -7952,7 +7951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>46223</v>
       </c>
@@ -7972,7 +7971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>46223</v>
       </c>
@@ -7992,7 +7991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>46223</v>
       </c>
@@ -8012,7 +8011,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>46223</v>
       </c>
@@ -8032,7 +8031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>46223</v>
       </c>
@@ -8052,7 +8051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>46223</v>
       </c>
@@ -8072,7 +8071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>46224</v>
       </c>
@@ -8092,7 +8091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>46224</v>
       </c>
@@ -8112,7 +8111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>46224</v>
       </c>
@@ -8132,7 +8131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>46224</v>
       </c>
@@ -8152,7 +8151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="385" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>46224</v>
       </c>
@@ -8172,7 +8171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="386" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>46224</v>
       </c>
@@ -8190,6 +8189,306 @@
       </c>
       <c r="F386" s="3" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F387" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F388" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F389" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F390" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F391" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F393" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F394" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F395" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F396" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F397" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F398" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F399" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F400" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F401" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G401"/>
+  <dimension ref="A1:G403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14453,6 +14453,76 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>414</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>415</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G403"/>
+  <dimension ref="A1:G410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14523,6 +14523,251 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>416</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>417</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>418</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>419</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>420</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>421</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>422</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G410"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14768,6 +14768,251 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>423</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>424</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>425</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>426</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>427</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>428</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>429</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -14484,7 +14484,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14799,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14869,7 +14869,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rouge</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>bleu</t>
         </is>
       </c>
     </row>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G417"/>
+  <dimension ref="A1:G422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15013,6 +15013,181 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>439</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>440</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>442</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>443</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>444</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G422"/>
+  <dimension ref="A1:G430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15188,6 +15188,286 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>446</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>447</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>448</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>449</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>450</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>451</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>454</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>455</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G430"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15468,6 +15468,181 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>458</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>459</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>460</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>461</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>462</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15643,6 +15643,111 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>463</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>464</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>465</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15748,6 +15748,41 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>466</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G439"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15783,6 +15783,181 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>467</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>468</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>469</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>470</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>471</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15958,6 +15958,111 @@
         </is>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>472</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>473</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>474</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G447"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16063,6 +16063,216 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>475</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>476</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>477</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>478</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>479</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>480</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G453"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16273,6 +16273,216 @@
         </is>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>481</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>482</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>483</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>484</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>485</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>486</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G459"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16483,6 +16483,181 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>487</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>488</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>489</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>490</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>491</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16658,6 +16658,76 @@
         </is>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>492</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>493</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G466"/>
+  <dimension ref="A1:G468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16728,6 +16728,76 @@
         </is>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>494</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>495</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G468"/>
+  <dimension ref="A1:G469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16798,6 +16798,41 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>496</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G469"/>
+  <dimension ref="A1:G475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16833,6 +16833,216 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>497</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>498</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>499</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>500</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>501</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>502</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G475"/>
+  <dimension ref="A1:G479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17043,6 +17043,146 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>503</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>504</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>505</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>506</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G479"/>
+  <dimension ref="A1:G484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17183,6 +17183,181 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>507</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>508</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>509</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>510</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>511</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G484"/>
+  <dimension ref="A1:G489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17358,6 +17358,181 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>512</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>513</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>514</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>515</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>516</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G489"/>
+  <dimension ref="A1:G491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17533,6 +17533,76 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>517</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>518</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G491"/>
+  <dimension ref="A1:G495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17603,6 +17603,146 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>519</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>520</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>521</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>522</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G495"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17743,6 +17743,181 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>523</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>524</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>525</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>526</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>527</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17918,6 +17918,146 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>528</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>529</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>PhilippeA</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>530</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>531</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>PhilippeA</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G504"/>
+  <dimension ref="A1:G510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18058,6 +18058,216 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>532</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>533</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>534</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>535</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>536</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>537</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G510"/>
+  <dimension ref="A1:G517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18268,6 +18268,251 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>538</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>539</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>PhilippeA</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>540</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>541</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>542</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>543</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>544</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G517"/>
+  <dimension ref="A1:G522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18513,6 +18513,181 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>545</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>546</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>547</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>548</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>549</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G522"/>
+  <dimension ref="A1:G529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18688,6 +18688,251 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>550</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>551</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>552</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>PhilippeA</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>553</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>554</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>556</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>557</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G529"/>
+  <dimension ref="A1:G536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18933,6 +18933,251 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>558</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>559</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>560</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>561</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>562</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>563</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>564</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G536"/>
+  <dimension ref="A1:G540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19178,6 +19178,146 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>565</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>566</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>567</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>568</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G540"/>
+  <dimension ref="A1:G542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19318,6 +19318,76 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>569</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>570</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19388,6 +19388,181 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>571</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>572</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>573</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>574</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>575</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G547"/>
+  <dimension ref="A1:G549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19563,6 +19563,76 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>576</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>577</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G549"/>
+  <dimension ref="A1:G554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19633,6 +19633,181 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>578</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>JulienF</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>579</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>580</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>581</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>582</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G554"/>
+  <dimension ref="A1:G558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19808,6 +19808,146 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>583</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>584</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>585</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>586</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G558"/>
+  <dimension ref="A1:G564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19948,6 +19948,216 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>587</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>588</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>589</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>590</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>591</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>592</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G564"/>
+  <dimension ref="A1:G569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20158,6 +20158,181 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>593</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>595</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>596</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>597</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>598</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G569"/>
+  <dimension ref="A1:G574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20333,6 +20333,181 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>599</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>600</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>601</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>602</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>603</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G574"/>
+  <dimension ref="A1:G576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20508,6 +20508,76 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>604</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>605</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G576"/>
+  <dimension ref="A1:G580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20578,6 +20578,146 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>606</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>607</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>608</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>609</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G580"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20718,6 +20718,426 @@
         </is>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>610</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>611</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>612</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>613</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>614</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>615</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>616</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>617</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>618</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>619</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>620</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>621</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21138,6 +21138,111 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>622</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>623</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>624</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G595"/>
+  <dimension ref="A1:G602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21243,6 +21243,251 @@
         </is>
       </c>
     </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>625</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>626</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>627</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>628</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>629</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>630</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>631</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G602"/>
+  <dimension ref="A1:G609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21488,6 +21488,251 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>632</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>633</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>634</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>635</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>636</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>637</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>638</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G609"/>
+  <dimension ref="A1:G617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21733,6 +21733,286 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>639</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>640</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>641</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>642</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>643</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>644</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>645</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>646</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G617"/>
+  <dimension ref="A1:G628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22013,6 +22013,391 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>647</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>648</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>649</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>650</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>651</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>652</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>653</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>654</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>655</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>656</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>657</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G628"/>
+  <dimension ref="A1:G629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22398,6 +22398,41 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>658</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G629"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22433,6 +22433,216 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>659</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>660</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>661</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>662</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>663</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>664</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22643,6 +22643,181 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>665</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>666</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>667</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>668</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>670</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G640"/>
+  <dimension ref="A1:G644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22818,6 +22818,146 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>671</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>672</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>673</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>674</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G644"/>
+  <dimension ref="A1:G648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22958,6 +22958,146 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>675</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>676</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>677</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>678</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G648"/>
+  <dimension ref="A1:G652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23098,6 +23098,146 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>679</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>680</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>681</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>682</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
